--- a/src/attributions/attributions_ig_traj_436.xlsx
+++ b/src/attributions/attributions_ig_traj_436.xlsx
@@ -999,133 +999,133 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.06502513867310633</v>
+        <v>-0.03866816615555144</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01471546955056435</v>
+        <v>0.004504239593317197</v>
       </c>
       <c r="D2" t="n">
         <v>-0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.03064309682235732</v>
+        <v>0.01243296542947434</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2149764684642502</v>
+        <v>0.03778583868875188</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
         <v>-0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.3579147131063479</v>
+        <v>-0.2114910383117866</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1268713302264114</v>
+        <v>0.07190992538274638</v>
       </c>
       <c r="M2" t="n">
         <v>-0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1662921225465936</v>
+        <v>0.0245583076388708</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3465897591687563</v>
+        <v>0.1100554954535723</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1236975144862981</v>
+        <v>0.0107531439327706</v>
       </c>
       <c r="U2" t="n">
-        <v>0.003454373340785433</v>
+        <v>0.06597461789516097</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.2491626474162694</v>
+        <v>-0.08052153464065435</v>
       </c>
       <c r="X2" t="n">
         <v>-0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1573832497670477</v>
+        <v>-0.112709963107644</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.2122674737255187</v>
+        <v>-0.07940906555349894</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.02005931301461526</v>
+        <v>0.06335738499301063</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.1279705261641923</v>
+        <v>0.02816329717603985</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.1910627594079731</v>
+        <v>-0.09481733242527396</v>
       </c>
       <c r="AI2" t="n">
         <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.07204268153211602</v>
+        <v>-0.2278252140525076</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.04018476773372642</v>
+        <v>-0.01388223002721028</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.1491335795790864</v>
+        <v>-0.1760307643817594</v>
       </c>
       <c r="AP2" t="n">
         <v>-0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.1357076800847526</v>
+        <v>-0.1482121054048547</v>
       </c>
       <c r="AR2" t="n">
         <v>-0</v>
@@ -1137,22 +1137,22 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.3906339100896247</v>
+        <v>-0.3238840688508173</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.0702300543071912</v>
+        <v>-0.03997742970894874</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.04941137969596154</v>
+        <v>-0.05740063810374968</v>
       </c>
       <c r="AY2" t="n">
         <v>-0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.5260541586838751</v>
+        <v>0.0476520869683263</v>
       </c>
       <c r="BA2" t="n">
         <v>-0</v>
@@ -1164,22 +1164,22 @@
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.04856785824988079</v>
+        <v>-0.01017434412933734</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.04465492032005361</v>
+        <v>0.007806595901450877</v>
       </c>
       <c r="BF2" t="n">
         <v>-0</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.01060017493990203</v>
+        <v>0.05772313623684332</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.04676601943756878</v>
+        <v>0.03580049787245034</v>
       </c>
       <c r="BJ2" t="n">
         <v>-0</v>
@@ -1191,49 +1191,49 @@
         <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.1036209965342796</v>
+        <v>0.1905077438077478</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0.01839103105206491</v>
+        <v>0.05300956524333254</v>
       </c>
       <c r="BO2" t="n">
         <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.1014296694336283</v>
+        <v>0.1083847369330618</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0.1315142097321457</v>
+        <v>-0.1645459821805762</v>
       </c>
       <c r="BS2" t="n">
         <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.1620291606125625</v>
+        <v>-0.07467223945468086</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.2014570807835853</v>
+        <v>0.04055491294347115</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.06425069177364266</v>
+        <v>-0.06529473295088936</v>
       </c>
       <c r="BZ2" t="n">
         <v>-0</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.2910894048274854</v>
+        <v>0.09651263961541286</v>
       </c>
       <c r="CB2" t="n">
         <v>0</v>
@@ -1242,79 +1242,79 @@
         <v>-0</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.1695539095361147</v>
+        <v>0.1392533665254135</v>
       </c>
       <c r="CF2" t="n">
-        <v>-0.03500201352320778</v>
+        <v>-0.03654049605032631</v>
       </c>
       <c r="CG2" t="n">
         <v>0</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.003496526860332695</v>
+        <v>0.007353973833689843</v>
       </c>
       <c r="CI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0.1862253620536815</v>
+        <v>-0.01577615916231438</v>
       </c>
       <c r="CK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL2" t="n">
         <v>0</v>
       </c>
       <c r="CM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.03319901493886276</v>
+        <v>0.07047257933022888</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.01260381242733487</v>
+        <v>-0.03146800118980337</v>
       </c>
       <c r="CP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.02532996148895657</v>
+        <v>-0.05691982573919593</v>
       </c>
       <c r="CR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.04640034999799181</v>
+        <v>-0.02472257246403744</v>
       </c>
       <c r="CT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU2" t="n">
         <v>0</v>
       </c>
       <c r="CV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.1293410395051263</v>
+        <v>0.1312370954337868</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0.009239863972270017</v>
+        <v>-0.03459128543076976</v>
       </c>
       <c r="CY2" t="n">
         <v>-0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.03274355681309522</v>
+        <v>0.008164063372953754</v>
       </c>
       <c r="DA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB2" t="n">
-        <v>-0.1914126874887634</v>
+        <v>-0.02144515323010115</v>
       </c>
       <c r="DC2" t="n">
         <v>-0</v>
@@ -1323,79 +1323,79 @@
         <v>-0</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.2269160802304924</v>
+        <v>0.07138510703918477</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.1262744894750193</v>
+        <v>-0.06260119506477049</v>
       </c>
       <c r="DH2" t="n">
         <v>-0</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.01741468475741682</v>
+        <v>-0.1694561703759515</v>
       </c>
       <c r="DJ2" t="n">
         <v>0</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0.218616898828904</v>
+        <v>-0.0669527499319363</v>
       </c>
       <c r="DL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN2" t="n">
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.02746115451516166</v>
+        <v>0.02296048318549251</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.04304630712170977</v>
+        <v>-0.06704302177982259</v>
       </c>
       <c r="DQ2" t="n">
         <v>-0</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.07344779056266167</v>
+        <v>0.01881028173815228</v>
       </c>
       <c r="DS2" t="n">
         <v>-0</v>
       </c>
       <c r="DT2" t="n">
-        <v>-0.01163221042246901</v>
+        <v>-0.04508271887494433</v>
       </c>
       <c r="DU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.2043100863364314</v>
+        <v>0.09398782035898283</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.1120498481239024</v>
+        <v>0.07093912902769135</v>
       </c>
       <c r="DZ2" t="n">
         <v>0</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.0254053047103809</v>
+        <v>0.01013415320548445</v>
       </c>
       <c r="EB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC2" t="n">
-        <v>-0.01547198727102827</v>
+        <v>0.1113919957005504</v>
       </c>
       <c r="ED2" t="n">
         <v>0</v>
@@ -1404,25 +1404,25 @@
         <v>-0</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.071748718066901</v>
+        <v>0.1902262127154949</v>
       </c>
       <c r="EH2" t="n">
-        <v>-0.07000848417456661</v>
+        <v>0.008051512054115348</v>
       </c>
       <c r="EI2" t="n">
         <v>0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.1682869510239599</v>
+        <v>0.01966863132157323</v>
       </c>
       <c r="EK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL2" t="n">
-        <v>-0.2453138616082037</v>
+        <v>-0.01236567043360238</v>
       </c>
       <c r="EM2" t="n">
         <v>0</v>
@@ -1431,55 +1431,55 @@
         <v>0</v>
       </c>
       <c r="EO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.1207685846168054</v>
+        <v>0.05409329766772829</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.1645135078829458</v>
+        <v>0.05294651896503932</v>
       </c>
       <c r="ER2" t="n">
         <v>0</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.1325293478611282</v>
+        <v>-0.06633810839514509</v>
       </c>
       <c r="ET2" t="n">
         <v>-0</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0.1329313386988665</v>
+        <v>-0.05579775085775057</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW2" t="n">
         <v>0</v>
       </c>
       <c r="EX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.1327037270671927</v>
+        <v>0.1439889754057938</v>
       </c>
       <c r="EZ2" t="n">
-        <v>-0.01141682150139973</v>
+        <v>-0.04041327084307151</v>
       </c>
       <c r="FA2" t="n">
         <v>0</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.02536495273449735</v>
+        <v>0.03174339047446256</v>
       </c>
       <c r="FC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0.1893677930938509</v>
+        <v>-0.02291696990950538</v>
       </c>
       <c r="FE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF2" t="n">
         <v>0</v>
@@ -1488,64 +1488,64 @@
         <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.03984527099657786</v>
+        <v>0.06080830331280549</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.2507110276468437</v>
+        <v>0.1944393619351893</v>
       </c>
       <c r="FJ2" t="n">
         <v>-0</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.0469606026909961</v>
+        <v>0.1118086427160725</v>
       </c>
       <c r="FL2" t="n">
         <v>0</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.07392660791540066</v>
+        <v>0.07836342037957993</v>
       </c>
       <c r="FN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.05555020898249854</v>
+        <v>0.3062550801277001</v>
       </c>
       <c r="FR2" t="n">
-        <v>-0.153170471291635</v>
+        <v>-0.004498056666243433</v>
       </c>
       <c r="FS2" t="n">
         <v>0</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.1689040024591716</v>
+        <v>0.2046171723240982</v>
       </c>
       <c r="FU2" t="n">
         <v>0</v>
       </c>
       <c r="FV2" t="n">
-        <v>-0.03719828958388986</v>
+        <v>-0.1055550598735089</v>
       </c>
       <c r="FW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX2" t="n">
         <v>0</v>
       </c>
       <c r="FY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.1438261524938854</v>
+        <v>0.1645098453007411</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.1637830150226</v>
+        <v>0.127949066758536</v>
       </c>
       <c r="GB2" t="n">
         <v>0</v>
@@ -1554,13 +1554,13 @@
         <v>-0</v>
       </c>
       <c r="GD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE2" t="n">
-        <v>-0.1008196875798051</v>
+        <v>0.0546451408212553</v>
       </c>
       <c r="GF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG2" t="n">
         <v>0</v>
@@ -2706,25 +2706,25 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1912735103841556</v>
+        <v>0.001164696671779172</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.04084455705163806</v>
+        <v>-0.000313710914716877</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.04545403757662421</v>
+        <v>-0.0002075527650104361</v>
       </c>
       <c r="H5" t="n">
         <v>-0</v>
@@ -2736,157 +2736,157 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2803607755609194</v>
+        <v>0.004002716162878388</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.07073462907228821</v>
+        <v>-0.0005342096188541835</v>
       </c>
       <c r="O5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.09661569076723513</v>
+        <v>-0.001541685567922381</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5" t="n">
         <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.135185987245995</v>
+        <v>-5.450247416974183e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1253135378798622</v>
+        <v>-0.00214263728765154</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.0427903332531837</v>
+        <v>7.061134015816165e-05</v>
       </c>
       <c r="Z5" t="n">
         <v>-0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1011859424637583</v>
+        <v>-0.001835442132047832</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.07214026667210552</v>
+        <v>-0.002809807739901601</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.003504962578441376</v>
+        <v>-0.00052339582446853</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0621761594674141</v>
+        <v>0.000313563714032609</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.02748846071119561</v>
+        <v>3.012952310697882e-05</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.04051434933252168</v>
+        <v>-0.0003487936221258189</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT5" t="n">
         <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.3458589130608589</v>
+        <v>0.006350952756667225</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.169715555613633</v>
+        <v>0.0002244155812783547</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.189899742043436</v>
+        <v>-0.0003819253941060979</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.015855322325043</v>
+        <v>-0.0005669954289761138</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF5" t="n">
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.05291389349662001</v>
+        <v>-0.0004867228839493639</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.00582107246823356</v>
+        <v>-6.591430723174325e-05</v>
       </c>
       <c r="BJ5" t="n">
         <v>-0</v>
@@ -2898,22 +2898,22 @@
         <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.08942450746987574</v>
+        <v>0.001766625613427673</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.08184788975443601</v>
+        <v>0.002707884455740626</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.07914186445190051</v>
+        <v>-0.001164129942831739</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,88 +2925,88 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1745142873007227</v>
+        <v>0.003562766694434082</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.121430457362074</v>
+        <v>0.0001441840597723474</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.1063661299560261</v>
+        <v>-0.0001647570372278709</v>
       </c>
       <c r="CB5" t="n">
         <v>-0</v>
       </c>
       <c r="CC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.1081562484577258</v>
+        <v>-0.0005442764994526285</v>
       </c>
       <c r="CF5" t="n">
         <v>0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.02018773784696388</v>
+        <v>0.0001650742113882199</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.0418350523507978</v>
+        <v>0.0002825068875992212</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL5" t="n">
         <v>-0</v>
       </c>
       <c r="CM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.001550487513381433</v>
+        <v>-0.001687780083891759</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.1068222940572895</v>
+        <v>-0.0006771860675906399</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.006391095180075561</v>
+        <v>-3.622565994776245e-05</v>
       </c>
       <c r="CT5" t="n">
         <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.110196556348984</v>
+        <v>-0.0006098217911702953</v>
       </c>
       <c r="CX5" t="n">
         <v>-0</v>
@@ -3015,13 +3015,13 @@
         <v>0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.002900741950183282</v>
+        <v>-0.0001785950167349344</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.05778661935190642</v>
+        <v>0.000531932470444263</v>
       </c>
       <c r="DC5" t="n">
         <v>0</v>
@@ -3033,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.1061553488764212</v>
+        <v>-0.001939466875270684</v>
       </c>
       <c r="DG5" t="n">
         <v>-0</v>
@@ -3042,25 +3042,25 @@
         <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.08884937412808847</v>
+        <v>-0.001686002592945352</v>
       </c>
       <c r="DJ5" t="n">
         <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.01534491169546844</v>
+        <v>-0.0002393388748287611</v>
       </c>
       <c r="DL5" t="n">
         <v>-0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.04729090126219514</v>
+        <v>-1.528954684493996e-05</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
@@ -3069,40 +3069,40 @@
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.02028978714310616</v>
+        <v>0.001152933930227776</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.00348809277158767</v>
+        <v>0.001362169347549009</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.1496798608581828</v>
+        <v>-0.0001182884138212213</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.03646951466540589</v>
+        <v>-0.001456747704069181</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.02718189712854432</v>
+        <v>0.001592244978497723</v>
       </c>
       <c r="ED5" t="n">
         <v>-0</v>
@@ -3111,10 +3111,10 @@
         <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.04811291961364726</v>
+        <v>-0.0004802721412025616</v>
       </c>
       <c r="EH5" t="n">
         <v>0</v>
@@ -3123,16 +3123,16 @@
         <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.03061398321258614</v>
+        <v>-0.000456545393957828</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.06932316469481034</v>
+        <v>-0.0002706787609869897</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
@@ -3141,22 +3141,22 @@
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.07901745033243264</v>
+        <v>-0.0007517989883432827</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
         <v>-0</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.04615082579383911</v>
+        <v>-0.0001394136038038334</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.04446956146828126</v>
+        <v>0.001291349585109913</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
@@ -3165,25 +3165,25 @@
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.1114162330789485</v>
+        <v>-0.001166666797788376</v>
       </c>
       <c r="EZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.01357562123999267</v>
+        <v>-0.0003339213682905175</v>
       </c>
       <c r="FC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.05936417113864469</v>
+        <v>0.0004237424914976374</v>
       </c>
       <c r="FE5" t="n">
         <v>-0</v>
@@ -3192,85 +3192,85 @@
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.001664469114917209</v>
+        <v>0.000923018007170621</v>
       </c>
       <c r="FI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.05752105311081148</v>
+        <v>-0.0003351215364254266</v>
       </c>
       <c r="FL5" t="n">
         <v>0</v>
       </c>
       <c r="FM5" t="n">
-        <v>-0.0002427519925802553</v>
+        <v>-0.0003810698888343422</v>
       </c>
       <c r="FN5" t="n">
         <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.01203323637238252</v>
+        <v>1.223895281333078e-05</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS5" t="n">
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.003212125092114352</v>
+        <v>2.156711217566126e-05</v>
       </c>
       <c r="FU5" t="n">
         <v>-0</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.04972060335476991</v>
+        <v>0.0007719386466306763</v>
       </c>
       <c r="FW5" t="n">
         <v>-0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.03667395536405726</v>
+        <v>-0.0002832953378658241</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
         <v>-0</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
-        <v>-0.001173731784051535</v>
+        <v>0.001207110029177101</v>
       </c>
       <c r="GF5" t="n">
         <v>-0</v>
       </c>
       <c r="GG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="6">
@@ -3847,25 +3847,25 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2773018009095569</v>
+        <v>0.2792809537738262</v>
       </c>
       <c r="C7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1709319222750238</v>
+        <v>-0.2543330767490219</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002124643523529515</v>
+        <v>-0.01466330416972467</v>
       </c>
       <c r="F7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3874,22 +3874,22 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3232767553547445</v>
+        <v>0.4652514332793957</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2078766579173851</v>
+        <v>-0.3483201567821722</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.03614070769266522</v>
+        <v>-0.07345403059767081</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -3898,25 +3898,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1735673972154964</v>
+        <v>0.1827553007564542</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.004358890417944773</v>
+        <v>-0.05449505129363538</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1201238304873656</v>
+        <v>-0.05203375481231412</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -3925,52 +3925,52 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.06800955915483413</v>
+        <v>-0.05812612587925828</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.001650293322489391</v>
+        <v>-0.1647903494721331</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.03099140077530024</v>
+        <v>-0.08198740723147799</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.01897181084112438</v>
+        <v>0.2217015183633945</v>
       </c>
       <c r="AM7" t="n">
         <v>-0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.1193032384038178</v>
+        <v>-0.09561617408287255</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.05232785611489597</v>
+        <v>0.1435399710924743</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -3982,43 +3982,43 @@
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.4327282137923817</v>
+        <v>0.467824016580777</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.04817787806375667</v>
+        <v>-0.2670640807847247</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.2474807712227255</v>
+        <v>-0.2593045635819618</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.02007841082537695</v>
+        <v>-0.0277690028205246</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.03967764650047999</v>
+        <v>-0.07675061248395207</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.04943501580789578</v>
+        <v>-0.02968668282119423</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4036,22 +4036,22 @@
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.01915629465322698</v>
+        <v>-0.05424145155177759</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.03294583971967385</v>
+        <v>0.1038883587259156</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.196660417829336</v>
+        <v>-0.01187713201607948</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
@@ -4063,49 +4063,49 @@
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.2127937552918518</v>
+        <v>0.4353936527988627</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.01566428378021673</v>
+        <v>-0.1624721324237433</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.1369888001597239</v>
+        <v>-0.06503228504357632</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.1109781378810753</v>
+        <v>-0.163514072400368</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.02960698295011292</v>
+        <v>0.2006241234620984</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.02274995539126169</v>
+        <v>-0.03129905686551407</v>
       </c>
       <c r="CI7" t="n">
         <v>0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
@@ -4117,19 +4117,19 @@
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.001436141899206497</v>
+        <v>-0.1128917697927835</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.1580173008842536</v>
+        <v>0.4488390600299961</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.1371855475670853</v>
+        <v>0.1968686702626515</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,28 +4138,28 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
         <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.1042740610638249</v>
+        <v>-0.1651153816358655</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.0584594873731383</v>
+        <v>0.2062751268991788</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.01178305334583765</v>
+        <v>-0.009000010715433727</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
@@ -4171,46 +4171,46 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.1325418903587163</v>
+        <v>-0.2122130093722615</v>
       </c>
       <c r="DG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.01949514869834752</v>
+        <v>0.09556023665957453</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.04284446953782638</v>
+        <v>-0.1213130215654498</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.00354377167525881</v>
+        <v>-0.0659531102463996</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.09352742489826868</v>
+        <v>0.04838532340397097</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.06475065613000254</v>
+        <v>-0.003461195094794747</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
@@ -4222,55 +4222,55 @@
         <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.04960892814370845</v>
+        <v>-0.02426373581130852</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.02449663297539604</v>
+        <v>-0.1377164974077984</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.04415507476923527</v>
+        <v>-0.1413263630001604</v>
       </c>
       <c r="EB7" t="n">
         <v>0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.113292483408766</v>
+        <v>-0.1365286507728611</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.02807679612274205</v>
+        <v>0.1806523126362186</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.08659808576004627</v>
+        <v>0.01487504616916792</v>
       </c>
       <c r="EK7" t="n">
         <v>0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
         <v>-0</v>
@@ -4279,25 +4279,25 @@
         <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.1138273587358946</v>
+        <v>-0.1344045821462058</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.07691172912582374</v>
+        <v>0.09716830177302492</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.002554645224206562</v>
+        <v>0.02204088379796691</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW7" t="n">
         <v>-0</v>
@@ -4306,22 +4306,22 @@
         <v>0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.1092153671339435</v>
+        <v>-0.2016192301139421</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.03163677736694261</v>
+        <v>0.2367580322776809</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.02283601585048151</v>
+        <v>-0.02709142013383754</v>
       </c>
       <c r="FC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
@@ -4330,82 +4330,82 @@
         <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.01285859735539381</v>
+        <v>-0.1585777441972887</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.09929373296947509</v>
+        <v>0.1697604865488151</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.03061584884253409</v>
+        <v>0.05964166477778963</v>
       </c>
       <c r="FL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM7" t="n">
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
         <v>0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.007802959727911293</v>
+        <v>-0.03565784586104882</v>
       </c>
       <c r="FR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.05124667113688459</v>
+        <v>0.05167629509974591</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.001529626720415848</v>
+        <v>0.03340981902715393</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.01881757638153156</v>
+        <v>-0.2236984665462727</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.1036454253051109</v>
+        <v>0.1420358940649089</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
         <v>-0</v>
@@ -4416,7 +4416,7 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1119061073808601</v>
+        <v>0.423743103670365</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -4425,13 +4425,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.02964204051597235</v>
+        <v>-0.01865129379146442</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0774026820496217</v>
+        <v>-0.1282169017590905</v>
       </c>
       <c r="G8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>-0</v>
@@ -4443,34 +4443,34 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1187681007878701</v>
+        <v>0.779798222203763</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.02848555426378352</v>
+        <v>-0.1548081140901623</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1594740987750541</v>
+        <v>-0.2121498981190229</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01471175716178471</v>
+        <v>0.2102830977930392</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -4479,94 +4479,94 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.03573368855965037</v>
+        <v>-0.1515405572929615</v>
       </c>
       <c r="X8" t="n">
-        <v>0.003569307520116752</v>
+        <v>-0.03072839041139061</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
         <v>-0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.02422355756365834</v>
+        <v>0.07070078549376664</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.01237014319306078</v>
+        <v>-0.3456449281947278</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.005353344881878945</v>
+        <v>-0.1677689979553316</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.01954382650047583</v>
+        <v>0.2850361646459985</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.02291212155421513</v>
+        <v>0.1162166810744311</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.03604989516040851</v>
+        <v>-0.1346000724955971</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS8" t="n">
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.1358727689925101</v>
+        <v>1.062232613133627</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.05256267994053983</v>
+        <v>-0.2420923637276466</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.1192505961073746</v>
+        <v>-0.2977358055002772</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA8" t="n">
         <v>0</v>
@@ -4578,7 +4578,7 @@
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.02885774680331783</v>
+        <v>-0.05161904353699988</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -4587,52 +4587,52 @@
         <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.01614988952648473</v>
+        <v>-0.0741293772045514</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.007826790542978131</v>
+        <v>-0.02514833149510656</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.04578808811915442</v>
+        <v>0.03517620693701538</v>
       </c>
       <c r="BN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.002721919169541816</v>
+        <v>0.1375332151992774</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.01776219413490068</v>
+        <v>-0.01450393873324311</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.06278986727875581</v>
+        <v>0.7069423119021679</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
@@ -4641,10 +4641,10 @@
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.015994167467405</v>
+        <v>-0.1092764787497396</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.04676285218861696</v>
+        <v>-0.210118806140225</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
@@ -4659,19 +4659,19 @@
         <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.03411697082092986</v>
+        <v>-0.2976812343916946</v>
       </c>
       <c r="CF8" t="n">
         <v>0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.002604890137771131</v>
+        <v>0.0344314602638801</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.04867661027729598</v>
+        <v>0.1565720225939929</v>
       </c>
       <c r="CJ8" t="n">
         <v>0</v>
@@ -4680,55 +4680,55 @@
         <v>0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.005809534617995238</v>
+        <v>-0.5648863571476197</v>
       </c>
       <c r="CO8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.01341125414828138</v>
+        <v>0.3245058383749325</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.02069943942371517</v>
+        <v>0.293212575876531</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT8" t="n">
         <v>-0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
         <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.02398853895093821</v>
+        <v>-0.2813361242634249</v>
       </c>
       <c r="CX8" t="n">
         <v>-0</v>
       </c>
       <c r="CY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.002938280795131109</v>
+        <v>0.000323591716640216</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.05276451868259511</v>
+        <v>0.1323900692112485</v>
       </c>
       <c r="DB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC8" t="n">
         <v>-0</v>
@@ -4740,19 +4740,19 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.0108241387501756</v>
+        <v>-0.03891750776490935</v>
       </c>
       <c r="DG8" t="n">
         <v>-0</v>
       </c>
       <c r="DH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.04431564764294891</v>
+        <v>-0.311730253456693</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.03028845269206921</v>
+        <v>-0.07873298390010842</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
@@ -4761,31 +4761,31 @@
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.01041242346621587</v>
+        <v>-0.1854827543320844</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.006202621719507907</v>
+        <v>0.1068000815400688</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.02094876644697482</v>
+        <v>0.04637613964539445</v>
       </c>
       <c r="DT8" t="n">
         <v>0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
@@ -4794,7 +4794,7 @@
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.01364671537720359</v>
+        <v>0.05526662964428825</v>
       </c>
       <c r="DY8" t="n">
         <v>0</v>
@@ -4803,16 +4803,16 @@
         <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.01349779066194938</v>
+        <v>0.07337197133102419</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0.03068989034804744</v>
+        <v>-0.1527152154465141</v>
       </c>
       <c r="EC8" t="n">
         <v>-0</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
         <v>-0</v>
@@ -4821,73 +4821,73 @@
         <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.03392422050990113</v>
+        <v>-0.05808594952309576</v>
       </c>
       <c r="EH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI8" t="n">
         <v>0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.007484974638955001</v>
+        <v>-0.108319849059039</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.02358499701266664</v>
+        <v>0.02768594446542784</v>
       </c>
       <c r="EL8" t="n">
         <v>-0</v>
       </c>
       <c r="EM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN8" t="n">
         <v>-0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.00666013788376032</v>
+        <v>-0.07039952729546708</v>
       </c>
       <c r="EQ8" t="n">
         <v>-0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.008091263963107213</v>
+        <v>-0.127323225071161</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.03587802974555144</v>
+        <v>0.02008711718746928</v>
       </c>
       <c r="EU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
       </c>
       <c r="EW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX8" t="n">
         <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.02181675826989959</v>
+        <v>-0.3128214513941078</v>
       </c>
       <c r="EZ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.006536945180870393</v>
+        <v>-0.0130459550547411</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.04832734798975944</v>
+        <v>0.1131154814184398</v>
       </c>
       <c r="FD8" t="n">
         <v>0</v>
@@ -4902,46 +4902,46 @@
         <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.02071897074804001</v>
+        <v>-0.3513462461315653</v>
       </c>
       <c r="FI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ8" t="n">
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.02325213095944769</v>
+        <v>0.1559486587445391</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.03090468164627593</v>
+        <v>0.1283002277604474</v>
       </c>
       <c r="FM8" t="n">
         <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.004676763264850553</v>
+        <v>-0.0866196214640113</v>
       </c>
       <c r="FR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS8" t="n">
         <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.00224202306191417</v>
+        <v>0.0202540573899633</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.04318108561725917</v>
+        <v>0.118752112890911</v>
       </c>
       <c r="FV8" t="n">
         <v>-0</v>
@@ -4950,13 +4950,13 @@
         <v>-0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.01183884360271291</v>
+        <v>-0.1372748442038295</v>
       </c>
       <c r="GA8" t="n">
         <v>0</v>
@@ -4968,13 +4968,13 @@
         <v>0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.03533705159214989</v>
+        <v>-0.05840964735925443</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG8" t="n">
         <v>0</v>
@@ -5551,64 +5551,64 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1695644144476582</v>
+        <v>0.006297526900594593</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1215150680338685</v>
+        <v>-0.002020938047176505</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.02111340195184868</v>
+        <v>-0.002061396878241401</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1702166929219318</v>
+        <v>0.01096932692127255</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.160313513031592</v>
+        <v>-0.0069930100907887</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1086574080189101</v>
+        <v>-0.007045235972344929</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1415757851362723</v>
+        <v>0.006402922548007524</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
@@ -5617,34 +5617,34 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.05294046119084305</v>
+        <v>-0.005784845994570294</v>
       </c>
       <c r="X10" t="n">
         <v>-0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.0335130414488258</v>
+        <v>-0.00313039538068808</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB10" t="n">
         <v>-0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.103884255443922</v>
+        <v>-0.004287873803910013</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.09460465614763876</v>
+        <v>-0.006882625282129584</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -5653,34 +5653,34 @@
         <v>-0</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.03753857880250319</v>
+        <v>0.0009819231263097899</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.07895486486987575</v>
+        <v>0.005030814642998971</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.07308108513732497</v>
+        <v>0.001058764207425698</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.02662611596864492</v>
+        <v>-0.0006896014922223355</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -5689,7 +5689,7 @@
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.3676604453216667</v>
+        <v>0.0145319765885762</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
@@ -5698,25 +5698,25 @@
         <v>-0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.0345846482843029</v>
+        <v>-0.001432851876644148</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ10" t="n">
         <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.1020559031703412</v>
+        <v>-0.004063099439866438</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.01482714182004296</v>
+        <v>-0.002269405822578259</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -5725,25 +5725,25 @@
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.07964234851312525</v>
+        <v>-0.004103300168167344</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-0.01982616584823643</v>
+        <v>-0.0001313815461919537</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL10" t="n">
         <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.1303080343157565</v>
+        <v>0.003456064045328003</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
@@ -5752,61 +5752,61 @@
         <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.1273285953242965</v>
+        <v>0.00757064832031362</v>
       </c>
       <c r="BQ10" t="n">
         <v>-0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.07291102541498046</v>
+        <v>0.003523540077042038</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU10" t="n">
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.2408428560122092</v>
+        <v>0.01279811599657738</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
         <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.008249238374271276</v>
+        <v>-0.0007769433901471188</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.05073984972084462</v>
+        <v>-0.005474881772084912</v>
       </c>
       <c r="CC10" t="n">
         <v>0</v>
       </c>
       <c r="CD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.05649848229335751</v>
+        <v>-0.002014795106458248</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
         <v>-0</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.02706257375124173</v>
+        <v>0.001988406443417173</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
@@ -5815,16 +5815,16 @@
         <v>-0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.007587977714496206</v>
+        <v>0.001559366885849153</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.09592347463077937</v>
+        <v>-0.003175251843328936</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
@@ -5833,34 +5833,34 @@
         <v>0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.1638837981304989</v>
+        <v>0.007684693882841384</v>
       </c>
       <c r="CR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>-0.01240342880811449</v>
+        <v>0.001720922201192581</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.04014284160072558</v>
+        <v>-0.002055506197121294</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.01064817579079889</v>
+        <v>0.002130285761334804</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
@@ -5869,70 +5869,70 @@
         <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>-0.006362382448172587</v>
+        <v>0.00284305325798173</v>
       </c>
       <c r="DD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.2178274646739015</v>
+        <v>-0.002215043402920227</v>
       </c>
       <c r="DG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.05736297695236896</v>
+        <v>0.001329971188535988</v>
       </c>
       <c r="DJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0.05417255741384178</v>
+        <v>0.0003578346821780259</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.03001173294825847</v>
+        <v>-0.003900409287970896</v>
       </c>
       <c r="DP10" t="n">
         <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.06111976535616231</v>
+        <v>-0.001489175208158825</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
         <v>0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.07077714105823922</v>
+        <v>0.0007897619876588858</v>
       </c>
       <c r="DV10" t="n">
         <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.07330185969311666</v>
+        <v>0.0031491614661363</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
@@ -5941,34 +5941,34 @@
         <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.001375336168628384</v>
+        <v>-0.003932015780464767</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.003340943540596913</v>
+        <v>-0.005619362702533382</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
         <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.02225209175060179</v>
+        <v>0.002690499258991867</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.04435149956788909</v>
+        <v>-0.001270764176184472</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
@@ -5977,16 +5977,16 @@
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.01700158444883986</v>
+        <v>-0.0007485322315294907</v>
       </c>
       <c r="EN10" t="n">
         <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.0003464553699039973</v>
+        <v>-0.001354111180708651</v>
       </c>
       <c r="EQ10" t="n">
         <v>0</v>
@@ -5995,34 +5995,34 @@
         <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.01955993567440947</v>
+        <v>-0.002006468216878455</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
         <v>-0</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0.01914613774411443</v>
+        <v>0.001500751398023037</v>
       </c>
       <c r="EW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.04026971739437694</v>
+        <v>-0.002131156517021503</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.008306420124009036</v>
+        <v>0.0003897697271089237</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
@@ -6031,43 +6031,43 @@
         <v>-0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.008047909376652175</v>
+        <v>0.002669829846996096</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.02225815511910279</v>
+        <v>0.001183770450251161</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.004820057813897297</v>
+        <v>0.005010939010119433</v>
       </c>
       <c r="FL10" t="n">
         <v>0</v>
       </c>
       <c r="FM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0.04693304821861666</v>
+        <v>-0.001594666668663744</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
         <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.001199493060553601</v>
+        <v>-0.0003835007583250586</v>
       </c>
       <c r="FR10" t="n">
         <v>-0</v>
@@ -6076,7 +6076,7 @@
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.008331984907812468</v>
+        <v>0.001148354574823593</v>
       </c>
       <c r="FU10" t="n">
         <v>0</v>
@@ -6085,19 +6085,19 @@
         <v>0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0.07852872037282509</v>
+        <v>0.002234787834495744</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.109350021632686</v>
+        <v>-0.004255658993512325</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
         <v>-0</v>
@@ -6106,13 +6106,13 @@
         <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF10" t="n">
-        <v>-0.07276329797423869</v>
+        <v>-0.00189305909155493</v>
       </c>
       <c r="GG10" t="n">
         <v>0</v>
@@ -6120,25 +6120,25 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0.1177698714293708</v>
+        <v>-0.1052742989531522</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3249752564862312</v>
+        <v>0.136161236286988</v>
       </c>
       <c r="C11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.151718453081389</v>
+        <v>-0.04140208772887639</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
         <v>-0</v>
@@ -6147,25 +6147,25 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.09192326391032815</v>
+        <v>-0.08346702805432882</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3017894514533932</v>
+        <v>0.2268843049877021</v>
       </c>
       <c r="L11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2640550751985269</v>
+        <v>-0.05754748407042976</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -6174,19 +6174,19 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01554456825218738</v>
+        <v>0.02700466972724636</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2405542190348784</v>
+        <v>0.0364536252583798</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1486571685804677</v>
+        <v>0.02207863722124756</v>
       </c>
       <c r="X11" t="n">
         <v>-0</v>
@@ -6195,31 +6195,31 @@
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.04312879386260491</v>
+        <v>-0.04977714213147276</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.141569984750978</v>
+        <v>-0.02429092972039974</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.05437778698158643</v>
+        <v>-0.06714295446432585</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>-0</v>
@@ -6228,10 +6228,10 @@
         <v>-0</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0.05750962004694525</v>
+        <v>-0.008580371393703427</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.1610901980328689</v>
+        <v>0.1050233408540257</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
@@ -6240,34 +6240,34 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.04925849284550114</v>
+        <v>-0.007922500828695656</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.1407057404946695</v>
+        <v>-0.007329724783327511</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.4392127026231664</v>
+        <v>0.1882765586076657</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.2036085458227275</v>
+        <v>-0.0666154617935515</v>
       </c>
       <c r="AY11" t="n">
         <v>0</v>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>-0.05523357514575405</v>
+        <v>-0.07247589084717083</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.03507317412798312</v>
+        <v>-0.0005049334607606454</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,25 +6294,25 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.2061355525993748</v>
+        <v>-0.0514735855027449</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0.02752323103099041</v>
+        <v>0.02580734523207404</v>
       </c>
       <c r="BM11" t="n">
-        <v>-0.02003646584046534</v>
+        <v>0.06229631788651486</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
@@ -6321,13 +6321,13 @@
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.1208013638998381</v>
+        <v>0.04582377697446182</v>
       </c>
       <c r="BQ11" t="n">
         <v>-0</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
@@ -6336,49 +6336,49 @@
         <v>-0</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.07227523953236691</v>
+        <v>0.02937773964209967</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.3051770644005236</v>
+        <v>0.1753873494614529</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.07106241098085622</v>
+        <v>-0.01112408392805903</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
         <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.0199102581058963</v>
+        <v>0.04859485875715949</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.09583553457955192</v>
+        <v>-0.08021667381006965</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.009572897401322574</v>
+        <v>0.008463303014828897</v>
       </c>
       <c r="CI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ11" t="n">
         <v>-0</v>
@@ -6390,10 +6390,10 @@
         <v>-0</v>
       </c>
       <c r="CM11" t="n">
-        <v>-0.1836329161309005</v>
+        <v>-0.01956236004279719</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.01959299996428621</v>
+        <v>-0.1383794123686853</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
@@ -6402,34 +6402,34 @@
         <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.1643425632976743</v>
+        <v>0.06260955057644454</v>
       </c>
       <c r="CR11" t="n">
         <v>-0</v>
       </c>
       <c r="CS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT11" t="n">
         <v>-0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.01217971553519494</v>
+        <v>0.03566740658179777</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.1005903010492936</v>
+        <v>-0.07652298958216831</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.008676440907185279</v>
+        <v>-0.005993112092909855</v>
       </c>
       <c r="DA11" t="n">
         <v>0</v>
@@ -6438,28 +6438,28 @@
         <v>0</v>
       </c>
       <c r="DC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD11" t="n">
         <v>0</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.1080623713875584</v>
+        <v>0.01126908682240155</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.2587886085915038</v>
+        <v>-0.1169718887025305</v>
       </c>
       <c r="DG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH11" t="n">
         <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.09318552878313725</v>
+        <v>-0.02054814283241482</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK11" t="n">
         <v>-0</v>
@@ -6468,13 +6468,13 @@
         <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN11" t="n">
-        <v>-0.08073664474910421</v>
+        <v>-0.02862637706910421</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.09453740344308463</v>
+        <v>-0.02880241557326988</v>
       </c>
       <c r="DP11" t="n">
         <v>-0</v>
@@ -6483,61 +6483,61 @@
         <v>-0</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.02458841430406961</v>
+        <v>0.004336095304465106</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU11" t="n">
         <v>-0</v>
       </c>
       <c r="DV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW11" t="n">
-        <v>-0.03115042677729704</v>
+        <v>0.06768505001996804</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.141402847967315</v>
+        <v>0.09226230626652777</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.08505250227120421</v>
+        <v>-0.02920961078559529</v>
       </c>
       <c r="EB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>-0.03801498935401587</v>
+        <v>0.004215082375329778</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.07130168173774544</v>
+        <v>-0.00734027048191527</v>
       </c>
       <c r="EH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI11" t="n">
         <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.01977181716631723</v>
+        <v>-0.02455980455048632</v>
       </c>
       <c r="EK11" t="n">
         <v>-0</v>
@@ -6549,22 +6549,22 @@
         <v>-0</v>
       </c>
       <c r="EN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO11" t="n">
-        <v>-0.02229985150782946</v>
+        <v>0.00419067760052901</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.09002744793433408</v>
+        <v>-0.05143190354550661</v>
       </c>
       <c r="EQ11" t="n">
         <v>0</v>
       </c>
       <c r="ER11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.008863210898384634</v>
+        <v>-0.02968569662954109</v>
       </c>
       <c r="ET11" t="n">
         <v>-0</v>
@@ -6579,25 +6579,25 @@
         <v>0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.01080461303996895</v>
+        <v>0.04471192042873697</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.1048638224331706</v>
+        <v>-0.09507586638666306</v>
       </c>
       <c r="EZ11" t="n">
         <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.02730788943885895</v>
+        <v>-0.01033471987585874</v>
       </c>
       <c r="FC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>-0</v>
@@ -6606,10 +6606,10 @@
         <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.08845141938396059</v>
+        <v>0.000641605742059793</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.03713189621380895</v>
+        <v>-0.01292566082769665</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
@@ -6618,52 +6618,52 @@
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.07646611775332582</v>
+        <v>-0.007893110839898651</v>
       </c>
       <c r="FL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP11" t="n">
-        <v>-0.04652254813282305</v>
+        <v>0.01744707058866332</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.02859300127721811</v>
+        <v>0.004940735671290115</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.001755154227389984</v>
+        <v>0.02633202108279676</v>
       </c>
       <c r="FU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0.07331234900531676</v>
+        <v>0.03525421765980274</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.06132199791436554</v>
+        <v>-0.05423951121537363</v>
       </c>
       <c r="GA11" t="n">
         <v>-0</v>
@@ -6672,10 +6672,10 @@
         <v>-0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6684,30 +6684,30 @@
         <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2058500451588145</v>
+        <v>0.01431743416001335</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.08870829256096012</v>
+        <v>-0.007865512194805272</v>
       </c>
       <c r="F12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2080093949240779</v>
+        <v>-0.006374849396147155</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -6716,28 +6716,28 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1290592541817942</v>
+        <v>0.02206449011315238</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1248583093041691</v>
+        <v>-0.008127611096269187</v>
       </c>
       <c r="O12" t="n">
         <v>-0</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1938639628999057</v>
+        <v>-0.0107192013570263</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -6746,76 +6746,76 @@
         <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1121043777129248</v>
+        <v>0.001606669240727231</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.187184719351781</v>
+        <v>-0.002711338495924937</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.07665819793054886</v>
+        <v>0.002184529621769968</v>
       </c>
       <c r="Z12" t="n">
         <v>-0</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1559524814782994</v>
+        <v>-0.001838015342551879</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.04995776987423239</v>
+        <v>-0.008487728278575551</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.02289454176627528</v>
+        <v>0.0005031484054540948</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ12" t="n">
         <v>-0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.02133836310122615</v>
+        <v>0.01066691076797092</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.03053373606623519</v>
+        <v>0.00299201959309568</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.08872361538481742</v>
+        <v>0.000828805951231065</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -6827,7 +6827,7 @@
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.3593675073590822</v>
+        <v>0.02769241621663224</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
@@ -6836,16 +6836,16 @@
         <v>-0</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.07021188671607284</v>
+        <v>-0.001153823138398501</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0.1421243878149263</v>
+        <v>-0.0005357681827409668</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
@@ -6854,7 +6854,7 @@
         <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.03948908518885419</v>
+        <v>-0.006006819567723565</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -6863,13 +6863,13 @@
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.05032996804159538</v>
+        <v>-0.005312035379927053</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>-0.08829291876180481</v>
+        <v>-0.001912912506280632</v>
       </c>
       <c r="BJ12" t="n">
         <v>0</v>
@@ -6878,25 +6878,25 @@
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.03217808466230792</v>
+        <v>-0.001648628227023323</v>
       </c>
       <c r="BN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO12" t="n">
         <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1720644772011463</v>
+        <v>0.009189537684082568</v>
       </c>
       <c r="BQ12" t="n">
         <v>-0</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.04947839128446527</v>
+        <v>0.004766572854743809</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
@@ -6905,52 +6905,52 @@
         <v>-0</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1175965335235025</v>
+        <v>0.0175224541174561</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.01855855689146976</v>
+        <v>-0.0009960419996873319</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>-0.08694323786912121</v>
+        <v>-0.0003869854487500026</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.07176028832982231</v>
+        <v>-0.007271172234235386</v>
       </c>
       <c r="CF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG12" t="n">
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.03273087617294767</v>
+        <v>0.002992322907239575</v>
       </c>
       <c r="CI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.04739165200533413</v>
+        <v>0.001497450038075997</v>
       </c>
       <c r="CK12" t="n">
         <v>-0</v>
@@ -6959,25 +6959,25 @@
         <v>-0</v>
       </c>
       <c r="CM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.1429192768740613</v>
+        <v>-0.01151751837298664</v>
       </c>
       <c r="CO12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.06991142460488214</v>
+        <v>-0.0005032920044213873</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
-        <v>-0.04686990460822364</v>
+        <v>-0.007080951324573124</v>
       </c>
       <c r="CT12" t="n">
         <v>-0</v>
@@ -6986,10 +6986,10 @@
         <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.05399582869366481</v>
+        <v>-0.00765080304642519</v>
       </c>
       <c r="CX12" t="n">
         <v>0</v>
@@ -6998,13 +6998,13 @@
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.02815143962453354</v>
+        <v>0.002696371823842836</v>
       </c>
       <c r="DA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.04634344306022908</v>
+        <v>0.002539647674273164</v>
       </c>
       <c r="DC12" t="n">
         <v>0</v>
@@ -7013,10 +7013,10 @@
         <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.2186637431555521</v>
+        <v>-0.003869395229875284</v>
       </c>
       <c r="DG12" t="n">
         <v>-0</v>
@@ -7025,67 +7025,67 @@
         <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.05967342391631554</v>
+        <v>-0.0003162222802876424</v>
       </c>
       <c r="DJ12" t="n">
         <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0.01983284543265945</v>
+        <v>-0.002904777551476721</v>
       </c>
       <c r="DL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM12" t="n">
         <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.007010996204414117</v>
+        <v>-0.002690182365175624</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.0457011479805482</v>
+        <v>0.002092339460752744</v>
       </c>
       <c r="DS12" t="n">
         <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>-0.03264941202275405</v>
+        <v>0.00411983894083775</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.09832486955054166</v>
+        <v>0.002910226565573386</v>
       </c>
       <c r="DY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ12" t="n">
         <v>-0</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.05632171611471885</v>
+        <v>-0.002409505987913742</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.02575850438193266</v>
+        <v>3.89856805375271e-06</v>
       </c>
       <c r="ED12" t="n">
         <v>0</v>
@@ -7094,25 +7094,25 @@
         <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.02333140949470254</v>
+        <v>-0.006930794544418158</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
         <v>-0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.05550733184227665</v>
+        <v>0.002705372032745628</v>
       </c>
       <c r="EK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.04886327960939023</v>
+        <v>-0.001509604394456036</v>
       </c>
       <c r="EM12" t="n">
         <v>-0</v>
@@ -7121,52 +7121,52 @@
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.02971580743030945</v>
+        <v>-0.003851763254776162</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
         <v>-0</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.0364389841099767</v>
+        <v>0.0008802246762867783</v>
       </c>
       <c r="ET12" t="n">
         <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.03256612396686034</v>
+        <v>-0.002381670614936278</v>
       </c>
       <c r="EV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.064220509306031</v>
+        <v>-0.008016079085694225</v>
       </c>
       <c r="EZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA12" t="n">
         <v>-0</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.03777303542492122</v>
+        <v>0.001106809681841859</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.03420764371482514</v>
+        <v>0.001338893688460821</v>
       </c>
       <c r="FE12" t="n">
         <v>-0</v>
@@ -7175,52 +7175,52 @@
         <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.02042340758147201</v>
+        <v>-0.003890637663222184</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.1036332821659217</v>
+        <v>-0.001476151929698857</v>
       </c>
       <c r="FL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.06614310036605796</v>
+        <v>-0.0007293723719030539</v>
       </c>
       <c r="FN12" t="n">
         <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.005871493921728364</v>
+        <v>-0.001498588551829633</v>
       </c>
       <c r="FR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS12" t="n">
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.006455618386448165</v>
+        <v>-0.0005706790791506416</v>
       </c>
       <c r="FU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.04970448626052981</v>
+        <v>0.004984896549558412</v>
       </c>
       <c r="FW12" t="n">
         <v>-0</v>
@@ -7229,13 +7229,13 @@
         <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.0758729608431695</v>
+        <v>-0.008068688805093788</v>
       </c>
       <c r="GA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB12" t="n">
         <v>-0</v>
@@ -7244,16 +7244,16 @@
         <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.125604245066121</v>
+        <v>0.001214391807290495</v>
       </c>
       <c r="GF12" t="n">
         <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.4455748330750715</v>
+        <v>1.175976480905355</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -7270,25 +7270,25 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.09724062926093466</v>
+        <v>-0.4997557326415378</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H13" t="n">
         <v>-0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2308289338686006</v>
+        <v>-0.170051936222704</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3241167543651432</v>
+        <v>1.69346794953826</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -7297,61 +7297,61 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1375868134705606</v>
+        <v>-0.6196519871369736</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.2488413136462798</v>
+        <v>-0.1472425031981172</v>
       </c>
       <c r="S13" t="n">
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1778425223659343</v>
+        <v>0.2590716062369993</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.07252730989160019</v>
+        <v>-0.2064360105417524</v>
       </c>
       <c r="X13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z13" t="n">
         <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.06564064848131686</v>
+        <v>-0.280707965663457</v>
       </c>
       <c r="AB13" t="n">
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.1802897194045926</v>
+        <v>0.1237885799162508</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.05445466802930047</v>
+        <v>-0.3448224075384123</v>
       </c>
       <c r="AG13" t="n">
         <v>-0</v>
@@ -7360,16 +7360,16 @@
         <v>-0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.01130092615466017</v>
+        <v>0.05164212256980067</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.1017375521504815</v>
+        <v>0.595686583855682</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
@@ -7378,34 +7378,34 @@
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.03211900870365894</v>
+        <v>0.2493539589734957</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS13" t="n">
-        <v>-0.02817387933415013</v>
+        <v>-0.0445651186170961</v>
       </c>
       <c r="AT13" t="n">
         <v>-0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.5743588276717405</v>
+        <v>1.958604343507415</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.1593362124157635</v>
+        <v>-0.3082652020140885</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
@@ -7414,16 +7414,16 @@
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>-0.160510241804709</v>
+        <v>0.01990338374863938</v>
       </c>
       <c r="BC13" t="n">
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.02896098931520412</v>
+        <v>-0.2805625963055416</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,79 +7432,79 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.1353084827021165</v>
+        <v>-0.3430856949661656</v>
       </c>
       <c r="BH13" t="n">
         <v>0</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0.09763271430333333</v>
+        <v>-0.05250341405010735</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>-0.01580162219568594</v>
+        <v>0.1195496534609469</v>
       </c>
       <c r="BN13" t="n">
         <v>-0</v>
       </c>
       <c r="BO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.1635777822005112</v>
+        <v>0.2779941786946895</v>
       </c>
       <c r="BQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.009774155310051857</v>
+        <v>0.2145191063875103</v>
       </c>
       <c r="BU13" t="n">
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.2982230561597482</v>
+        <v>1.278531319265363</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.07659603877682787</v>
+        <v>-0.1988541045190255</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB13" t="n">
         <v>-0</v>
       </c>
       <c r="CC13" t="n">
-        <v>-0.04912186303906273</v>
+        <v>-0.2402763110910193</v>
       </c>
       <c r="CD13" t="n">
         <v>0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.1220823420477336</v>
+        <v>-0.668439153011033</v>
       </c>
       <c r="CF13" t="n">
         <v>-0</v>
@@ -7513,37 +7513,37 @@
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.001127506267037298</v>
+        <v>0.1329879205646453</v>
       </c>
       <c r="CI13" t="n">
         <v>-0</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.08590252197647293</v>
+        <v>0.09081690812343314</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.1223337703651036</v>
+        <v>-1.007699644651398</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.1712786574668426</v>
+        <v>0.1283031385785063</v>
       </c>
       <c r="CR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS13" t="n">
         <v>-0</v>
@@ -7552,40 +7552,40 @@
         <v>-0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.004119869286127911</v>
+        <v>0.0273020493991433</v>
       </c>
       <c r="CV13" t="n">
         <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.112211203521746</v>
+        <v>-0.6410271279927588</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.003346368706697547</v>
+        <v>0.08463503338662044</v>
       </c>
       <c r="DA13" t="n">
         <v>0</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.06542903966920914</v>
+        <v>0.1486457194515638</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.2692720260715941</v>
+        <v>-0.3057968370567165</v>
       </c>
       <c r="DG13" t="n">
         <v>-0</v>
@@ -7594,7 +7594,7 @@
         <v>-0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.08987566310988837</v>
+        <v>-0.03653082927698079</v>
       </c>
       <c r="DJ13" t="n">
         <v>-0</v>
@@ -7606,22 +7606,22 @@
         <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>-0.04029221562578318</v>
+        <v>-0.1433942432812226</v>
       </c>
       <c r="DN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.004975079006561786</v>
+        <v>-0.3244669105775506</v>
       </c>
       <c r="DP13" t="n">
         <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.02656012849531851</v>
+        <v>0.0533853455488603</v>
       </c>
       <c r="DS13" t="n">
         <v>-0</v>
@@ -7630,43 +7630,43 @@
         <v>0</v>
       </c>
       <c r="DU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>-0.005760298206532577</v>
+        <v>-0.2528841180577492</v>
       </c>
       <c r="DW13" t="n">
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.1173781541030796</v>
+        <v>0.3856577270637193</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.02040877321491244</v>
+        <v>-0.1322410645459416</v>
       </c>
       <c r="EB13" t="n">
         <v>-0</v>
       </c>
       <c r="EC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.02089302542389034</v>
+        <v>0.2203234287375027</v>
       </c>
       <c r="EF13" t="n">
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.02444615292679015</v>
+        <v>-0.3502819211566084</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
@@ -7675,52 +7675,52 @@
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.01168185906914874</v>
+        <v>-0.02830175222775196</v>
       </c>
       <c r="EK13" t="n">
         <v>-0</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.1217655965465076</v>
+        <v>0.07463477975811106</v>
       </c>
       <c r="EO13" t="n">
         <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.09339807308311356</v>
+        <v>-0.4016665038071621</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.01977529898042384</v>
+        <v>0.04216038213397014</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU13" t="n">
         <v>0</v>
       </c>
       <c r="EV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.0003655899560750315</v>
+        <v>0.1392401718658015</v>
       </c>
       <c r="EX13" t="n">
         <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.1286442919128734</v>
+        <v>-0.7431514075962301</v>
       </c>
       <c r="EZ13" t="n">
         <v>-0</v>
@@ -7729,25 +7729,25 @@
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.01541905363081584</v>
+        <v>0.06691561934140565</v>
       </c>
       <c r="FC13" t="n">
         <v>-0</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>-0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.05715199691508521</v>
+        <v>0.1511532827783821</v>
       </c>
       <c r="FG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.09905271829711042</v>
+        <v>-0.2614733007744827</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
@@ -7756,25 +7756,25 @@
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.05784149357419523</v>
+        <v>-0.0418755612025313</v>
       </c>
       <c r="FL13" t="n">
         <v>0</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
         <v>0</v>
       </c>
       <c r="FO13" t="n">
-        <v>-0.05628812282743786</v>
+        <v>-0.2467089452650089</v>
       </c>
       <c r="FP13" t="n">
         <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.0165881721947123</v>
+        <v>-0.04009673883361592</v>
       </c>
       <c r="FR13" t="n">
         <v>0</v>
@@ -7783,46 +7783,46 @@
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.008102099971654579</v>
+        <v>0.04782565364131028</v>
       </c>
       <c r="FU13" t="n">
         <v>-0</v>
       </c>
       <c r="FV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW13" t="n">
         <v>-0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.01408669996251717</v>
+        <v>-0.2096553024822468</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.1345992625993349</v>
+        <v>-0.3349347594331124</v>
       </c>
       <c r="GA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC13" t="n">
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0.02360812263165026</v>
+        <v>0.184409891811564</v>
       </c>
     </row>
     <row r="14">
@@ -8399,16 +8399,16 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.5907795004285801</v>
+        <v>0.9365146217546055</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.3989518623425137</v>
+        <v>-0.36698646767343</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.09252403475631246</v>
+        <v>-0.4822573350252943</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -8426,25 +8426,25 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5050626613200868</v>
+        <v>1.355056608016393</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.3262444670309252</v>
+        <v>-0.4195472886320393</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2854567558636711</v>
+        <v>-0.4495753325069974</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P15" t="n">
         <v>-0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -8453,16 +8453,16 @@
         <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1897807471320398</v>
+        <v>0.2159707552699376</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.02029988754024378</v>
+        <v>0.05032126059056551</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.05652242697967574</v>
+        <v>0.1710523632106212</v>
       </c>
       <c r="X15" t="n">
         <v>-0</v>
@@ -8471,61 +8471,61 @@
         <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.1870684611749188</v>
+        <v>0.0934146366518931</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.02204934376175902</v>
+        <v>-0.232144218729458</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.08347761226110914</v>
+        <v>-0.1595711027299697</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ15" t="n">
         <v>-0</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.2841163628792014</v>
+        <v>0.5378763822698424</v>
       </c>
       <c r="AM15" t="n">
-        <v>-0.05471824795404803</v>
+        <v>-0.07881765481103624</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.03370583471837622</v>
+        <v>0.352146558983805</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS15" t="n">
         <v>0</v>
@@ -8534,46 +8534,46 @@
         <v>-0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.594231962697403</v>
+        <v>1.424558932205944</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0.2836455096055909</v>
+        <v>0.02175646268956084</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.0448668381595007</v>
+        <v>-0.1236868439798693</v>
       </c>
       <c r="AY15" t="n">
         <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
         <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.08768484298742456</v>
+        <v>-0.3188106329442574</v>
       </c>
       <c r="BE15" t="n">
-        <v>-0.1961871347644716</v>
+        <v>-0.4052738089750161</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.2311621508018974</v>
+        <v>-0.4527181783523483</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI15" t="n">
         <v>-0</v>
@@ -8588,22 +8588,22 @@
         <v>-0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.07998463931774845</v>
+        <v>0.04693917913765383</v>
       </c>
       <c r="BN15" t="n">
-        <v>-0.1097685112961139</v>
+        <v>-0.1121152541091886</v>
       </c>
       <c r="BO15" t="n">
         <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.1815055184834277</v>
+        <v>0.1873737864602174</v>
       </c>
       <c r="BQ15" t="n">
         <v>-0</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
         <v>-0</v>
@@ -8615,16 +8615,16 @@
         <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.2913806926080225</v>
+        <v>0.9494316544219833</v>
       </c>
       <c r="BW15" t="n">
-        <v>-0.3333410508698076</v>
+        <v>-0.01678020670608184</v>
       </c>
       <c r="BX15" t="n">
         <v>0</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.04983374037369032</v>
+        <v>0.07100172850784824</v>
       </c>
       <c r="BZ15" t="n">
         <v>-0</v>
@@ -8636,22 +8636,22 @@
         <v>0</v>
       </c>
       <c r="CC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD15" t="n">
         <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.1457715073897463</v>
+        <v>-0.5152431760776065</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.02825468931812659</v>
+        <v>0.1445441635075595</v>
       </c>
       <c r="CG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.04169400559116405</v>
+        <v>0.1425682938701682</v>
       </c>
       <c r="CI15" t="n">
         <v>-0</v>
@@ -8660,7 +8660,7 @@
         <v>-0</v>
       </c>
       <c r="CK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL15" t="n">
         <v>-0</v>
@@ -8669,19 +8669,19 @@
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.01343093360960241</v>
+        <v>-0.7800025004215969</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.004829513798193239</v>
+        <v>0.1519079675755408</v>
       </c>
       <c r="CP15" t="n">
         <v>-0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.1020621569983537</v>
+        <v>0.143146335501231</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS15" t="n">
         <v>-0</v>
@@ -8690,22 +8690,22 @@
         <v>-0</v>
       </c>
       <c r="CU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV15" t="n">
         <v>0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.1113453844271666</v>
+        <v>-0.4728542432137779</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.023447008917863</v>
+        <v>0.1256213314076539</v>
       </c>
       <c r="CY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.01852341139202471</v>
+        <v>0.06381029183325246</v>
       </c>
       <c r="DA15" t="n">
         <v>0</v>
@@ -8714,7 +8714,7 @@
         <v>0</v>
       </c>
       <c r="DC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD15" t="n">
         <v>0</v>
@@ -8723,19 +8723,19 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.1390887419599823</v>
+        <v>-0.2126469244350246</v>
       </c>
       <c r="DG15" t="n">
-        <v>-0.03086037292576049</v>
+        <v>0.1005652905265351</v>
       </c>
       <c r="DH15" t="n">
         <v>-0</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0.08493861221327145</v>
+        <v>0.04752213050369274</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK15" t="n">
         <v>0</v>
@@ -8750,76 +8750,76 @@
         <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.03764789556508622</v>
+        <v>-0.218478273900943</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.01780961237692205</v>
+        <v>-0.0769336848568784</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.008507041442613095</v>
+        <v>0.1748404244072458</v>
       </c>
       <c r="DS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT15" t="n">
         <v>0</v>
       </c>
       <c r="DU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV15" t="n">
         <v>0</v>
       </c>
       <c r="DW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.06126441155205174</v>
+        <v>0.4768483412469247</v>
       </c>
       <c r="DY15" t="n">
-        <v>-0.08511085627849853</v>
+        <v>0.1091478265519565</v>
       </c>
       <c r="DZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA15" t="n">
-        <v>-0.0374450718513996</v>
+        <v>-0.2950860273810009</v>
       </c>
       <c r="EB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC15" t="n">
         <v>0</v>
       </c>
       <c r="ED15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE15" t="n">
         <v>-0</v>
       </c>
       <c r="EF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.04720303651469306</v>
+        <v>-0.2666433279694633</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.009759931043592501</v>
+        <v>-0.07414586466872955</v>
       </c>
       <c r="EI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.07792833050205475</v>
+        <v>0.03629709892042642</v>
       </c>
       <c r="EK15" t="n">
         <v>-0</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
         <v>-0</v>
@@ -8828,73 +8828,73 @@
         <v>-0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.04595661248020445</v>
+        <v>-0.2861788245028098</v>
       </c>
       <c r="EQ15" t="n">
-        <v>-0.1106715498472844</v>
+        <v>0.01884129927641989</v>
       </c>
       <c r="ER15" t="n">
         <v>0</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.09452568183755154</v>
+        <v>0.02092507477301015</v>
       </c>
       <c r="ET15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU15" t="n">
         <v>-0</v>
       </c>
       <c r="EV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW15" t="n">
         <v>-0</v>
       </c>
       <c r="EX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.122824575399272</v>
+        <v>-0.548207205864621</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.01994690641237671</v>
+        <v>0.1406168951059909</v>
       </c>
       <c r="FA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.051329521421728</v>
+        <v>0.08809449166332801</v>
       </c>
       <c r="FC15" t="n">
         <v>-0</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF15" t="n">
         <v>-0</v>
       </c>
       <c r="FG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.1029617169823601</v>
+        <v>-0.05271776779285079</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0.1329469674295655</v>
+        <v>-0.3627503379210645</v>
       </c>
       <c r="FJ15" t="n">
         <v>-0</v>
       </c>
       <c r="FK15" t="n">
-        <v>-0.1432798239022791</v>
+        <v>-0.3055291169483746</v>
       </c>
       <c r="FL15" t="n">
         <v>0</v>
@@ -8903,64 +8903,64 @@
         <v>0</v>
       </c>
       <c r="FN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP15" t="n">
         <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.000766764666897827</v>
+        <v>-0.00268875143762271</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.05550624530852524</v>
+        <v>0.03923289660652526</v>
       </c>
       <c r="FS15" t="n">
         <v>-0</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.01517693923645303</v>
+        <v>0.03679882405287955</v>
       </c>
       <c r="FU15" t="n">
         <v>-0</v>
       </c>
       <c r="FV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.06162526306120281</v>
+        <v>-0.353030292530732</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.01277318649842005</v>
+        <v>-0.2232207995590363</v>
       </c>
       <c r="GB15" t="n">
         <v>-0</v>
       </c>
       <c r="GC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE15" t="n">
         <v>-0</v>
       </c>
       <c r="GF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -8968,7 +8968,7 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.5025994176302351</v>
+        <v>0.3545828212686763</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -8977,7 +8977,7 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.03234233613095101</v>
+        <v>-0.1991372222818531</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -8989,13 +8989,13 @@
         <v>-0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3243190074281432</v>
+        <v>-0.07419528011378325</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3543559262263809</v>
+        <v>0.5317029307753016</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -9004,79 +9004,79 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0727056060268471</v>
+        <v>-0.2997101625788739</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.2544294435558138</v>
+        <v>-0.1087512605346057</v>
       </c>
       <c r="S16" t="n">
         <v>-0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1131928689981723</v>
+        <v>0.02708640547414473</v>
       </c>
       <c r="U16" t="n">
         <v>-0</v>
       </c>
       <c r="V16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.006154694897210576</v>
+        <v>-0.1083912036825737</v>
       </c>
       <c r="X16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.07613652471431498</v>
+        <v>-0.01983309517795192</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.1703138451986171</v>
+        <v>-0.01383370403387296</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.04153114115060682</v>
+        <v>-0.1039956246144523</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0.02424773754708348</v>
+        <v>0.008421021044543406</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.09552635091293049</v>
+        <v>0.1370047909112817</v>
       </c>
       <c r="AM16" t="n">
         <v>0</v>
@@ -9085,52 +9085,52 @@
         <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.0005930179846301423</v>
+        <v>-0.02358799507556461</v>
       </c>
       <c r="AP16" t="n">
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS16" t="n">
-        <v>-0.07882455555996977</v>
+        <v>0.02203366721596657</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.4523337567415014</v>
+        <v>0.4707223109756103</v>
       </c>
       <c r="AV16" t="n">
         <v>-0</v>
       </c>
       <c r="AW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.1517605598065375</v>
+        <v>-0.1740839964733349</v>
       </c>
       <c r="AY16" t="n">
         <v>-0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>-0.1404093262725181</v>
+        <v>0.01019495527010819</v>
       </c>
       <c r="BC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.07501628806493117</v>
+        <v>-0.04270679360592765</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
@@ -9139,25 +9139,25 @@
         <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.1799295426076874</v>
+        <v>-0.07260411051813248</v>
       </c>
       <c r="BH16" t="n">
         <v>0</v>
       </c>
       <c r="BI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
-        <v>-0.17491429587882</v>
+        <v>-0.05963286244787001</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.01855901654884917</v>
+        <v>0.09122587435082521</v>
       </c>
       <c r="BN16" t="n">
         <v>-0</v>
@@ -9166,52 +9166,52 @@
         <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.15363148965093</v>
+        <v>0.1283736531319084</v>
       </c>
       <c r="BQ16" t="n">
         <v>-0</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
         <v>-0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0.01282564579733253</v>
+        <v>0.0404346239193179</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.2584867140468766</v>
+        <v>0.3065848694895895</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.06779278497354253</v>
+        <v>-0.1499550881630424</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC16" t="n">
-        <v>-0.05439368754766404</v>
+        <v>-0.04060977199928734</v>
       </c>
       <c r="CD16" t="n">
         <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.1063051417888271</v>
+        <v>-0.1412784218516184</v>
       </c>
       <c r="CF16" t="n">
         <v>-0</v>
@@ -9220,37 +9220,37 @@
         <v>-0</v>
       </c>
       <c r="CH16" t="n">
-        <v>-0.0123999375250363</v>
+        <v>0.05352478956169792</v>
       </c>
       <c r="CI16" t="n">
         <v>-0</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
         <v>0</v>
       </c>
       <c r="CL16" t="n">
-        <v>0.08241951422047439</v>
+        <v>0.02610441452158619</v>
       </c>
       <c r="CM16" t="n">
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.06478893541454656</v>
+        <v>-0.2385129047129514</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
       </c>
       <c r="CP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.04621327902943281</v>
+        <v>0.02715975222447897</v>
       </c>
       <c r="CR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS16" t="n">
         <v>-0</v>
@@ -9259,40 +9259,40 @@
         <v>-0</v>
       </c>
       <c r="CU16" t="n">
-        <v>-0.02343245301141927</v>
+        <v>-0.004458144553206122</v>
       </c>
       <c r="CV16" t="n">
         <v>0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.09414416943103228</v>
+        <v>-0.1312277601510701</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
         <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>-0.01914849684373003</v>
+        <v>0.02975361429624733</v>
       </c>
       <c r="DA16" t="n">
         <v>0</v>
       </c>
       <c r="DB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD16" t="n">
-        <v>0.07504276223898444</v>
+        <v>0.02891599637899607</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.1182261744395655</v>
+        <v>-0.02961034249346532</v>
       </c>
       <c r="DG16" t="n">
         <v>-0</v>
@@ -9301,7 +9301,7 @@
         <v>-0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.05412685565158881</v>
+        <v>-0.1041828483442449</v>
       </c>
       <c r="DJ16" t="n">
         <v>-0</v>
@@ -9313,121 +9313,121 @@
         <v>-0</v>
       </c>
       <c r="DM16" t="n">
-        <v>0.03219904337586417</v>
+        <v>-0.07614706244463255</v>
       </c>
       <c r="DN16" t="n">
         <v>-0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.01423163962202957</v>
+        <v>-0.08493573190070969</v>
       </c>
       <c r="DP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.006994885417896802</v>
+        <v>0.001160407161428532</v>
       </c>
       <c r="DS16" t="n">
         <v>-0</v>
       </c>
       <c r="DT16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV16" t="n">
-        <v>-0.02374782169982614</v>
+        <v>-0.01407654548936669</v>
       </c>
       <c r="DW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>0.07353167572043219</v>
+        <v>0.08934021868537179</v>
       </c>
       <c r="DY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA16" t="n">
-        <v>-0.04227195418086139</v>
+        <v>0.009800844020228808</v>
       </c>
       <c r="EB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC16" t="n">
         <v>-0</v>
       </c>
       <c r="ED16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE16" t="n">
-        <v>0.02796226645634012</v>
+        <v>0.05777962240642723</v>
       </c>
       <c r="EF16" t="n">
         <v>0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.03077529897577023</v>
+        <v>-0.0401055623449924</v>
       </c>
       <c r="EH16" t="n">
         <v>0</v>
       </c>
       <c r="EI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>-0.0004336784504817793</v>
+        <v>-0.01607858878486162</v>
       </c>
       <c r="EK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM16" t="n">
         <v>0</v>
       </c>
       <c r="EN16" t="n">
-        <v>0.1036915773196381</v>
+        <v>0.01758761521123939</v>
       </c>
       <c r="EO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0.1056797150948331</v>
+        <v>-0.05795361737981648</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
         <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>-0.03259428197368409</v>
+        <v>0.009872192204333264</v>
       </c>
       <c r="ET16" t="n">
         <v>-0</v>
       </c>
       <c r="EU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW16" t="n">
-        <v>-0.04756516615355748</v>
+        <v>0.06013705484805655</v>
       </c>
       <c r="EX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.1178670650332119</v>
+        <v>-0.1606725163840855</v>
       </c>
       <c r="EZ16" t="n">
         <v>-0</v>
@@ -9436,25 +9436,25 @@
         <v>-0</v>
       </c>
       <c r="FB16" t="n">
-        <v>-0.02715481701731032</v>
+        <v>0.02255678963357994</v>
       </c>
       <c r="FC16" t="n">
         <v>-0</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF16" t="n">
-        <v>0.0646619709015803</v>
+        <v>0.03855766347935955</v>
       </c>
       <c r="FG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.06191831366897853</v>
+        <v>-0.08349358399901825</v>
       </c>
       <c r="FI16" t="n">
         <v>-0</v>
@@ -9463,7 +9463,7 @@
         <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>-0.055576272012112</v>
+        <v>0.09201888681952491</v>
       </c>
       <c r="FL16" t="n">
         <v>0</v>
@@ -9475,40 +9475,40 @@
         <v>0</v>
       </c>
       <c r="FO16" t="n">
-        <v>0.02139657467474632</v>
+        <v>0.0642152391244718</v>
       </c>
       <c r="FP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0.00148086181662483</v>
+        <v>-0.002262050785536415</v>
       </c>
       <c r="FR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.000504162863575076</v>
+        <v>0.002046802179052992</v>
       </c>
       <c r="FU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW16" t="n">
         <v>-0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0.01357506348458504</v>
+        <v>-0.00094535526774349</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>-0.05419168035346556</v>
+        <v>-0.04100032024613815</v>
       </c>
       <c r="GA16" t="n">
         <v>0</v>
@@ -9517,27 +9517,27 @@
         <v>-0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE16" t="n">
         <v>-0</v>
       </c>
       <c r="GF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG16" t="n">
-        <v>0.005116448674482819</v>
+        <v>0.06198528855676559</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-0.1450283934898477</v>
+        <v>-0.02372056941707217</v>
       </c>
       <c r="B17" t="n">
-        <v>0.3062561047424777</v>
+        <v>0.04131643732160385</v>
       </c>
       <c r="C17" t="n">
         <v>-0</v>
@@ -9546,7 +9546,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.004364620054611141</v>
+        <v>-0.02162038146857253</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -9555,16 +9555,16 @@
         <v>-0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1332743239940226</v>
+        <v>-0.01825916109202654</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2873678197897083</v>
+        <v>0.06852518384885566</v>
       </c>
       <c r="L17" t="n">
         <v>-0</v>
@@ -9573,7 +9573,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.08368245261017246</v>
+        <v>-0.02477424798838624</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9588,25 +9588,25 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.005902332190468476</v>
+        <v>0.005536596808011051</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1031246008266935</v>
+        <v>0.01158359640925321</v>
       </c>
       <c r="U17" t="n">
         <v>-0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.05699720229877055</v>
+        <v>-0.001027120168831855</v>
       </c>
       <c r="X17" t="n">
         <v>-0</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -9615,52 +9615,52 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.02586191543692579</v>
+        <v>0.002113451911267596</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.1138783956977097</v>
+        <v>-0.00432959099537644</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.01371311578678623</v>
+        <v>-0.004875089248281705</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>-0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>-0.01677649799122805</v>
+        <v>0.0002488613279908987</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.07775943758745023</v>
+        <v>0.01269946676217871</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.05098910888926177</v>
+        <v>-0.007202944514552173</v>
       </c>
       <c r="AP17" t="n">
         <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR17" t="n">
         <v>-0</v>
@@ -9669,37 +9669,37 @@
         <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>-0.0239761537076614</v>
+        <v>-0.006753489854071193</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.2680415258520715</v>
+        <v>0.03777836907702553</v>
       </c>
       <c r="AV17" t="n">
         <v>-0</v>
       </c>
       <c r="AW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.2275944397392204</v>
+        <v>-0.02405494863417618</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
         <v>-0</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>-0.06963962924390511</v>
+        <v>-0.01696380532700793</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.01245205525493021</v>
+        <v>0.008083584745928411</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
@@ -9708,25 +9708,25 @@
         <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.1533763950412602</v>
+        <v>-0.01641288060446598</v>
       </c>
       <c r="BH17" t="n">
         <v>0</v>
       </c>
       <c r="BI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
       </c>
       <c r="BL17" t="n">
-        <v>-0.06101163327465105</v>
+        <v>-0.001556419968043042</v>
       </c>
       <c r="BM17" t="n">
-        <v>-0.02274610606011445</v>
+        <v>0.01139177698831306</v>
       </c>
       <c r="BN17" t="n">
         <v>-0</v>
@@ -9735,13 +9735,13 @@
         <v>-0</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.01391576317500381</v>
+        <v>0.03067270109513913</v>
       </c>
       <c r="BQ17" t="n">
         <v>-0</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
         <v>-0</v>
@@ -9750,25 +9750,25 @@
         <v>-0</v>
       </c>
       <c r="BU17" t="n">
-        <v>0.01501444647920728</v>
+        <v>0.005778395511794299</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.1683472121580763</v>
+        <v>0.03486235087994485</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.0507792668290547</v>
+        <v>-0.008083963932858986</v>
       </c>
       <c r="BZ17" t="n">
         <v>-0</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB17" t="n">
         <v>0</v>
@@ -9777,19 +9777,19 @@
         <v>0</v>
       </c>
       <c r="CD17" t="n">
-        <v>0.04000007307173718</v>
+        <v>0.00846789383597101</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.05453818036973004</v>
+        <v>-0.01321815831414361</v>
       </c>
       <c r="CF17" t="n">
         <v>-0</v>
       </c>
       <c r="CG17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH17" t="n">
-        <v>-0.03840247409659924</v>
+        <v>0.007228785096199225</v>
       </c>
       <c r="CI17" t="n">
         <v>-0</v>
@@ -9804,10 +9804,10 @@
         <v>-0</v>
       </c>
       <c r="CM17" t="n">
-        <v>-0.03781898321579104</v>
+        <v>-0.002237155044846617</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.01379031628086412</v>
+        <v>-0.03146331233344878</v>
       </c>
       <c r="CO17" t="n">
         <v>-0</v>
@@ -9816,10 +9816,10 @@
         <v>0</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.1213706244010509</v>
+        <v>0.0173253199075242</v>
       </c>
       <c r="CR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS17" t="n">
         <v>-0</v>
@@ -9831,19 +9831,19 @@
         <v>0</v>
       </c>
       <c r="CV17" t="n">
-        <v>0.02352082975433117</v>
+        <v>0.007046897657787903</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.06245390504132654</v>
+        <v>-0.01393856912233623</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
         <v>0</v>
       </c>
       <c r="CZ17" t="n">
-        <v>-0.02894768230131029</v>
+        <v>0.003075994520562241</v>
       </c>
       <c r="DA17" t="n">
         <v>0</v>
@@ -9858,19 +9858,19 @@
         <v>0</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.03547785053168344</v>
+        <v>0.005639751979740029</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.09648272798232696</v>
+        <v>-0.03194025957013532</v>
       </c>
       <c r="DG17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH17" t="n">
         <v>0</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0.007177448380538715</v>
+        <v>0.0002073957861581678</v>
       </c>
       <c r="DJ17" t="n">
         <v>0</v>
@@ -9879,16 +9879,16 @@
         <v>-0</v>
       </c>
       <c r="DL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM17" t="n">
         <v>-0</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.02277124310493113</v>
+        <v>0.003302379888104384</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.0129358505656151</v>
+        <v>-0.009453250971730776</v>
       </c>
       <c r="DP17" t="n">
         <v>-0</v>
@@ -9897,7 +9897,7 @@
         <v>-0</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.04261667835639647</v>
+        <v>-0.009034407493439462</v>
       </c>
       <c r="DS17" t="n">
         <v>-0</v>
@@ -9909,13 +9909,13 @@
         <v>-0</v>
       </c>
       <c r="DV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.01520493498490725</v>
+        <v>0.007143814600959794</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.0593548273950997</v>
+        <v>0.01605696866330404</v>
       </c>
       <c r="DY17" t="n">
         <v>0</v>
@@ -9924,25 +9924,25 @@
         <v>0</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.01296338099423119</v>
+        <v>-0.003915224126056376</v>
       </c>
       <c r="EB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC17" t="n">
         <v>-0</v>
       </c>
       <c r="ED17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE17" t="n">
         <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>-0.01039572169350779</v>
+        <v>-0.001743608811522281</v>
       </c>
       <c r="EG17" t="n">
-        <v>0.001263226131389152</v>
+        <v>-0.002427774456461721</v>
       </c>
       <c r="EH17" t="n">
         <v>-0</v>
@@ -9951,7 +9951,7 @@
         <v>0</v>
       </c>
       <c r="EJ17" t="n">
-        <v>-0.02461621833527135</v>
+        <v>0.0008238929763544519</v>
       </c>
       <c r="EK17" t="n">
         <v>-0</v>
@@ -9960,16 +9960,16 @@
         <v>-0</v>
       </c>
       <c r="EM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN17" t="n">
         <v>-0</v>
       </c>
       <c r="EO17" t="n">
-        <v>0.0106854152706513</v>
+        <v>0.00199075505787367</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.1025026239040847</v>
+        <v>0.003082732789867499</v>
       </c>
       <c r="EQ17" t="n">
         <v>-0</v>
@@ -9978,7 +9978,7 @@
         <v>0</v>
       </c>
       <c r="ES17" t="n">
-        <v>-0.03902147905849932</v>
+        <v>-0.00755196132686958</v>
       </c>
       <c r="ET17" t="n">
         <v>-0</v>
@@ -9987,16 +9987,16 @@
         <v>-0</v>
       </c>
       <c r="EV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX17" t="n">
-        <v>0.02330788700807145</v>
+        <v>0.009125890362272611</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.0744448865289912</v>
+        <v>-0.01738714511535258</v>
       </c>
       <c r="EZ17" t="n">
         <v>-0</v>
@@ -10005,7 +10005,7 @@
         <v>-0</v>
       </c>
       <c r="FB17" t="n">
-        <v>-0.06868372175746276</v>
+        <v>0.002798290972606765</v>
       </c>
       <c r="FC17" t="n">
         <v>-0</v>
@@ -10020,22 +10020,22 @@
         <v>-0</v>
       </c>
       <c r="FG17" t="n">
-        <v>0.02140080285614447</v>
+        <v>0.004204356067796225</v>
       </c>
       <c r="FH17" t="n">
-        <v>0.004955464002654584</v>
+        <v>-0.009197972184496719</v>
       </c>
       <c r="FI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ17" t="n">
         <v>-0</v>
       </c>
       <c r="FK17" t="n">
-        <v>-0.06706801856876159</v>
+        <v>0.0199435895328564</v>
       </c>
       <c r="FL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM17" t="n">
         <v>0</v>
@@ -10047,49 +10047,49 @@
         <v>-0</v>
       </c>
       <c r="FP17" t="n">
-        <v>0.0864534031141376</v>
+        <v>0.003260733313313482</v>
       </c>
       <c r="FQ17" t="n">
-        <v>-0.02326556006440409</v>
+        <v>0.001008745442009065</v>
       </c>
       <c r="FR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS17" t="n">
         <v>-0</v>
       </c>
       <c r="FT17" t="n">
-        <v>-0.004870107481667689</v>
+        <v>0.002357171552738183</v>
       </c>
       <c r="FU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX17" t="n">
         <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0.0320186217691341</v>
+        <v>0.01090995520939297</v>
       </c>
       <c r="FZ17" t="n">
-        <v>-0.0175993094740689</v>
+        <v>-0.01104206562405361</v>
       </c>
       <c r="GA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB17" t="n">
         <v>-0</v>
       </c>
       <c r="GC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE17" t="n">
         <v>-0</v>
@@ -10098,7 +10098,7 @@
         <v>-0</v>
       </c>
       <c r="GG17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -10106,49 +10106,49 @@
         <v>-0</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5070684835287268</v>
+        <v>0.1498876840207892</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1519953215431933</v>
+        <v>-0.1364141933736148</v>
       </c>
       <c r="F18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1769548735060516</v>
+        <v>-0.0181631556956894</v>
       </c>
       <c r="H18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3430387183262252</v>
+        <v>0.2064975568254803</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1549731854593712</v>
+        <v>-0.2092378522263859</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2009485741394578</v>
+        <v>-0.04940106228036183</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -10160,22 +10160,22 @@
         <v>-0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1369897935913975</v>
+        <v>0.07079550449098998</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.125510729472762</v>
+        <v>-0.009205968607524101</v>
       </c>
       <c r="X18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.01312121145246103</v>
+        <v>0.01523740754668955</v>
       </c>
       <c r="Z18" t="n">
         <v>-0</v>
@@ -10187,34 +10187,34 @@
         <v>-0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.1394273036977619</v>
+        <v>-0.02784208910394309</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>-0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.06253247594811912</v>
+        <v>-0.08371206247206253</v>
       </c>
       <c r="AG18" t="n">
         <v>-0</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0.02575009079944633</v>
+        <v>0.02193226356156847</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.04822317261119883</v>
+        <v>0.07053153116675775</v>
       </c>
       <c r="AM18" t="n">
         <v>-0</v>
@@ -10223,25 +10223,25 @@
         <v>-0</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.008666941256081645</v>
+        <v>0.01135144812868481</v>
       </c>
       <c r="AP18" t="n">
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>-0.03495606889012583</v>
+        <v>-0.01091747899311669</v>
       </c>
       <c r="AR18" t="n">
         <v>-0</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT18" t="n">
         <v>-0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.4414688501999068</v>
+        <v>0.21319796836691</v>
       </c>
       <c r="AV18" t="n">
         <v>-0</v>
@@ -10250,52 +10250,52 @@
         <v>-0</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.03498103781186453</v>
+        <v>-0.05404260259631689</v>
       </c>
       <c r="AY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>-0.122386106171035</v>
+        <v>-0.01071582486017519</v>
       </c>
       <c r="BA18" t="n">
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
         <v>-0</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.100733676612333</v>
+        <v>-0.06424938677928504</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG18" t="n">
-        <v>-0.05150113679389452</v>
+        <v>-0.05385332686866674</v>
       </c>
       <c r="BH18" t="n">
         <v>-0</v>
       </c>
       <c r="BI18" t="n">
-        <v>-0.08747455111042932</v>
+        <v>-0.02175083034753827</v>
       </c>
       <c r="BJ18" t="n">
         <v>-0</v>
       </c>
       <c r="BK18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.03325863507546089</v>
+        <v>0.01816080407422527</v>
       </c>
       <c r="BN18" t="n">
         <v>0</v>
@@ -10304,67 +10304,67 @@
         <v>-0</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.1244404288640718</v>
+        <v>0.09600022582213363</v>
       </c>
       <c r="BQ18" t="n">
         <v>-0</v>
       </c>
       <c r="BR18" t="n">
-        <v>-0.03947354190521901</v>
+        <v>0.03629434371017379</v>
       </c>
       <c r="BS18" t="n">
         <v>-0</v>
       </c>
       <c r="BT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU18" t="n">
         <v>-0</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.2018127536076341</v>
+        <v>0.1972814618110984</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>-0.01139150127486592</v>
+        <v>-0.02892477512729887</v>
       </c>
       <c r="BZ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA18" t="n">
-        <v>-0.06301471481279776</v>
+        <v>0.01196444297906586</v>
       </c>
       <c r="CB18" t="n">
         <v>-0</v>
       </c>
       <c r="CC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE18" t="n">
-        <v>-0.1078788746939449</v>
+        <v>-0.07219594852030808</v>
       </c>
       <c r="CF18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG18" t="n">
         <v>-0</v>
       </c>
       <c r="CH18" t="n">
-        <v>0.02996560589584826</v>
+        <v>0.0568909124444956</v>
       </c>
       <c r="CI18" t="n">
         <v>-0</v>
       </c>
       <c r="CJ18" t="n">
-        <v>0.05319002826730744</v>
+        <v>0.002275289988846612</v>
       </c>
       <c r="CK18" t="n">
         <v>-0</v>
@@ -10373,25 +10373,25 @@
         <v>-0</v>
       </c>
       <c r="CM18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN18" t="n">
-        <v>-0.1078420040983675</v>
+        <v>-0.1244590333355436</v>
       </c>
       <c r="CO18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ18" t="n">
-        <v>-0.1202469607854581</v>
+        <v>0.01769701983596822</v>
       </c>
       <c r="CR18" t="n">
         <v>0</v>
       </c>
       <c r="CS18" t="n">
-        <v>0.02886145479119778</v>
+        <v>0.0008410263261037112</v>
       </c>
       <c r="CT18" t="n">
         <v>-0</v>
@@ -10400,10 +10400,10 @@
         <v>-0</v>
       </c>
       <c r="CV18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW18" t="n">
-        <v>-0.09029384795738359</v>
+        <v>-0.06549972757007869</v>
       </c>
       <c r="CX18" t="n">
         <v>-0</v>
@@ -10412,13 +10412,13 @@
         <v>0</v>
       </c>
       <c r="CZ18" t="n">
-        <v>0.02866149027583024</v>
+        <v>0.05196406970298974</v>
       </c>
       <c r="DA18" t="n">
         <v>0</v>
       </c>
       <c r="DB18" t="n">
-        <v>0.03656536726165375</v>
+        <v>0.01558049705673411</v>
       </c>
       <c r="DC18" t="n">
         <v>0</v>
@@ -10427,28 +10427,28 @@
         <v>0</v>
       </c>
       <c r="DE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF18" t="n">
-        <v>-0.2628776269842755</v>
+        <v>-0.09255226131075805</v>
       </c>
       <c r="DG18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.04319878717753253</v>
+        <v>-0.01761381686275465</v>
       </c>
       <c r="DJ18" t="n">
         <v>-0</v>
       </c>
       <c r="DK18" t="n">
-        <v>-0.05513804135011058</v>
+        <v>-0.02782012491677582</v>
       </c>
       <c r="DL18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM18" t="n">
         <v>-0</v>
@@ -10457,7 +10457,7 @@
         <v>-0</v>
       </c>
       <c r="DO18" t="n">
-        <v>-0.03104925690354835</v>
+        <v>-0.02675991577104927</v>
       </c>
       <c r="DP18" t="n">
         <v>0</v>
@@ -10466,40 +10466,40 @@
         <v>0</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.007103100026380021</v>
+        <v>0.0563234503730474</v>
       </c>
       <c r="DS18" t="n">
         <v>-0</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.02356251419881231</v>
+        <v>0.01657187547259482</v>
       </c>
       <c r="DU18" t="n">
         <v>-0</v>
       </c>
       <c r="DV18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW18" t="n">
         <v>-0</v>
       </c>
       <c r="DX18" t="n">
-        <v>0.09428272573595585</v>
+        <v>0.05413266715387655</v>
       </c>
       <c r="DY18" t="n">
         <v>0</v>
       </c>
       <c r="DZ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA18" t="n">
-        <v>-0.06232901063393878</v>
+        <v>-0.05352780952281946</v>
       </c>
       <c r="EB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC18" t="n">
-        <v>-0.02341972319180255</v>
+        <v>-0.009665169472749882</v>
       </c>
       <c r="ED18" t="n">
         <v>0</v>
@@ -10508,25 +10508,25 @@
         <v>-0</v>
       </c>
       <c r="EF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG18" t="n">
-        <v>-0.07880185137472134</v>
+        <v>-0.03050618124029291</v>
       </c>
       <c r="EH18" t="n">
         <v>0</v>
       </c>
       <c r="EI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.05017273052686625</v>
+        <v>0.023933419586733</v>
       </c>
       <c r="EK18" t="n">
         <v>-0</v>
       </c>
       <c r="EL18" t="n">
-        <v>0.04341235960728476</v>
+        <v>-0.01143996112028552</v>
       </c>
       <c r="EM18" t="n">
         <v>-0</v>
@@ -10535,10 +10535,10 @@
         <v>-0</v>
       </c>
       <c r="EO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP18" t="n">
-        <v>-0.03067011551221096</v>
+        <v>-0.04836572236002094</v>
       </c>
       <c r="EQ18" t="n">
         <v>0</v>
@@ -10547,25 +10547,25 @@
         <v>-0</v>
       </c>
       <c r="ES18" t="n">
-        <v>0.0853738739473147</v>
+        <v>-0.006764729506276938</v>
       </c>
       <c r="ET18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU18" t="n">
-        <v>-0.03959466301732154</v>
+        <v>0.0190347454789135</v>
       </c>
       <c r="EV18" t="n">
         <v>-0</v>
       </c>
       <c r="EW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY18" t="n">
-        <v>-0.09231393266458732</v>
+        <v>-0.07537863319837283</v>
       </c>
       <c r="EZ18" t="n">
         <v>0</v>
@@ -10574,13 +10574,13 @@
         <v>-0</v>
       </c>
       <c r="FB18" t="n">
-        <v>0.02193125867806608</v>
+        <v>0.03977439090055263</v>
       </c>
       <c r="FC18" t="n">
         <v>-0</v>
       </c>
       <c r="FD18" t="n">
-        <v>0.03532723903125196</v>
+        <v>0.0002805137058748994</v>
       </c>
       <c r="FE18" t="n">
         <v>-0</v>
@@ -10592,34 +10592,34 @@
         <v>0</v>
       </c>
       <c r="FH18" t="n">
-        <v>-0.04400904787193322</v>
+        <v>-0.02977305192953052</v>
       </c>
       <c r="FI18" t="n">
         <v>-0</v>
       </c>
       <c r="FJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK18" t="n">
-        <v>-0.1127322733516995</v>
+        <v>-0.00238519507279046</v>
       </c>
       <c r="FL18" t="n">
         <v>-0</v>
       </c>
       <c r="FM18" t="n">
-        <v>0.02411277505497511</v>
+        <v>-0.02780115891472282</v>
       </c>
       <c r="FN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO18" t="n">
         <v>-0</v>
       </c>
       <c r="FP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>-0.009793930386886193</v>
+        <v>-0.004262832548478069</v>
       </c>
       <c r="FR18" t="n">
         <v>-0</v>
@@ -10628,13 +10628,13 @@
         <v>-0</v>
       </c>
       <c r="FT18" t="n">
-        <v>0.005182557770810742</v>
+        <v>-0.0006412981209867683</v>
       </c>
       <c r="FU18" t="n">
         <v>0</v>
       </c>
       <c r="FV18" t="n">
-        <v>-0.03051656735267664</v>
+        <v>-0.02823501201817321</v>
       </c>
       <c r="FW18" t="n">
         <v>0</v>
@@ -10643,31 +10643,31 @@
         <v>-0</v>
       </c>
       <c r="FY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>-0.05903719563294344</v>
+        <v>-0.04499924648852983</v>
       </c>
       <c r="GA18" t="n">
         <v>0</v>
       </c>
       <c r="GB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC18" t="n">
         <v>0</v>
       </c>
       <c r="GD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE18" t="n">
-        <v>0.001741469352806429</v>
+        <v>-0.009704480770243513</v>
       </c>
       <c r="GF18" t="n">
         <v>-0</v>
       </c>
       <c r="GG18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -11244,22 +11244,22 @@
         <v>0</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.1869573382331637</v>
+        <v>-0.3350511691159093</v>
       </c>
       <c r="C20" t="n">
         <v>-0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3023184592343354</v>
+        <v>0.2918784289450576</v>
       </c>
       <c r="E20" t="n">
-        <v>0.02272039432838016</v>
+        <v>0.2254039522531619</v>
       </c>
       <c r="F20" t="n">
         <v>-0</v>
       </c>
       <c r="G20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -11271,22 +11271,22 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1604474752503273</v>
+        <v>-0.3827618363625123</v>
       </c>
       <c r="L20" t="n">
         <v>-0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.327655719272808</v>
+        <v>0.4739374422213596</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1113456600398723</v>
+        <v>0.2812466117708723</v>
       </c>
       <c r="O20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -11295,73 +11295,73 @@
         <v>-0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.02691806874379581</v>
+        <v>-0.06079196189306236</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0.0143252989727879</v>
+        <v>0.05665734576829226</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1060886056445353</v>
+        <v>0.01158448582033745</v>
       </c>
       <c r="X20" t="n">
         <v>-0</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB20" t="n">
         <v>-0</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.04970619789400177</v>
+        <v>-0.0431379467496141</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.03045049329929172</v>
+        <v>0.07435637498327544</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.009733480363607931</v>
+        <v>-0.06540144884474253</v>
       </c>
       <c r="AG20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
         <v>-0</v>
       </c>
       <c r="AI20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>-0.05487763676867052</v>
+        <v>-0.2044893153308514</v>
       </c>
       <c r="AM20" t="n">
         <v>-0</v>
       </c>
       <c r="AN20" t="n">
-        <v>0.01266633104407108</v>
+        <v>0.03306437972438154</v>
       </c>
       <c r="AO20" t="n">
-        <v>-0.02272793854071766</v>
+        <v>-0.2128464081588029</v>
       </c>
       <c r="AP20" t="n">
         <v>-0</v>
@@ -11379,43 +11379,43 @@
         <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>-0.286873477679045</v>
+        <v>-0.5129365673541126</v>
       </c>
       <c r="AV20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.006458170809651075</v>
+        <v>0.09139728839416575</v>
       </c>
       <c r="AX20" t="n">
-        <v>-0.1412027336967856</v>
+        <v>0.130562653868143</v>
       </c>
       <c r="AY20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
         <v>-0</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD20" t="n">
-        <v>0.02976041038025856</v>
+        <v>0.09720357722809783</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF20" t="n">
-        <v>0.166452845645908</v>
+        <v>0.1108832940219397</v>
       </c>
       <c r="BG20" t="n">
-        <v>0.2375478576965494</v>
+        <v>0.1868910663891738</v>
       </c>
       <c r="BH20" t="n">
         <v>-0</v>
@@ -11424,7 +11424,7 @@
         <v>0</v>
       </c>
       <c r="BJ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK20" t="n">
         <v>-0</v>
@@ -11433,25 +11433,25 @@
         <v>0</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.0462724637641261</v>
+        <v>0.09804128808749345</v>
       </c>
       <c r="BN20" t="n">
         <v>0</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.03683820245122325</v>
+        <v>-0.01639128221932321</v>
       </c>
       <c r="BP20" t="n">
-        <v>-0.06523694290064841</v>
+        <v>-0.02221794239396222</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT20" t="n">
         <v>0</v>
@@ -11460,46 +11460,46 @@
         <v>0</v>
       </c>
       <c r="BV20" t="n">
-        <v>-0.1781186781916282</v>
+        <v>-0.3275335354724262</v>
       </c>
       <c r="BW20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX20" t="n">
-        <v>-0.01236493487917666</v>
+        <v>0.1823546921406823</v>
       </c>
       <c r="BY20" t="n">
-        <v>-0.008724332733459643</v>
+        <v>0.05967607341631333</v>
       </c>
       <c r="BZ20" t="n">
         <v>-0</v>
       </c>
       <c r="CA20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC20" t="n">
         <v>-0</v>
       </c>
       <c r="CD20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE20" t="n">
-        <v>0.04387018383907025</v>
+        <v>0.197888492854103</v>
       </c>
       <c r="CF20" t="n">
         <v>0</v>
       </c>
       <c r="CG20" t="n">
-        <v>-0.08760037473582617</v>
+        <v>-0.09492263242996703</v>
       </c>
       <c r="CH20" t="n">
-        <v>0.02148408688146284</v>
+        <v>-0.009942173313494781</v>
       </c>
       <c r="CI20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ20" t="n">
         <v>0</v>
@@ -11514,19 +11514,19 @@
         <v>-0</v>
       </c>
       <c r="CN20" t="n">
-        <v>-0.01388834498071505</v>
+        <v>0.1979153523244146</v>
       </c>
       <c r="CO20" t="n">
         <v>0</v>
       </c>
       <c r="CP20" t="n">
-        <v>-0.0215314864692131</v>
+        <v>-0.2525537709634357</v>
       </c>
       <c r="CQ20" t="n">
-        <v>-0.008018795035296396</v>
+        <v>-0.1126649565005415</v>
       </c>
       <c r="CR20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS20" t="n">
         <v>0</v>
@@ -11538,22 +11538,22 @@
         <v>0</v>
       </c>
       <c r="CV20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW20" t="n">
-        <v>0.05158609911742962</v>
+        <v>0.1977042645155877</v>
       </c>
       <c r="CX20" t="n">
         <v>-0</v>
       </c>
       <c r="CY20" t="n">
-        <v>-0.07684784951489181</v>
+        <v>-0.1054206641636186</v>
       </c>
       <c r="CZ20" t="n">
-        <v>0.001455367635933529</v>
+        <v>-0.03037319858350699</v>
       </c>
       <c r="DA20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB20" t="n">
         <v>-0</v>
@@ -11565,22 +11565,22 @@
         <v>-0</v>
       </c>
       <c r="DE20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF20" t="n">
-        <v>0.06348848124026969</v>
+        <v>0.04918202867661803</v>
       </c>
       <c r="DG20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH20" t="n">
-        <v>-0.0007436809931250562</v>
+        <v>-0.1105866557255497</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.04827039199911155</v>
+        <v>0.01849438182172237</v>
       </c>
       <c r="DJ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK20" t="n">
         <v>0</v>
@@ -11592,28 +11592,28 @@
         <v>-0</v>
       </c>
       <c r="DN20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO20" t="n">
-        <v>0.03755457765395096</v>
+        <v>0.0748858532914841</v>
       </c>
       <c r="DP20" t="n">
         <v>0</v>
       </c>
       <c r="DQ20" t="n">
-        <v>-0.1080578250472073</v>
+        <v>-0.05749779092765403</v>
       </c>
       <c r="DR20" t="n">
-        <v>-0.02462519411844031</v>
+        <v>0.07931142132178826</v>
       </c>
       <c r="DS20" t="n">
         <v>-0</v>
       </c>
       <c r="DT20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV20" t="n">
         <v>-0</v>
@@ -11622,52 +11622,52 @@
         <v>0</v>
       </c>
       <c r="DX20" t="n">
-        <v>-0.002575986165579502</v>
+        <v>-0.06854441440130991</v>
       </c>
       <c r="DY20" t="n">
         <v>0</v>
       </c>
       <c r="DZ20" t="n">
-        <v>0.01733143302964566</v>
+        <v>-0.06773619744201057</v>
       </c>
       <c r="EA20" t="n">
-        <v>-0.01297561302774764</v>
+        <v>-0.007867880610552883</v>
       </c>
       <c r="EB20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC20" t="n">
         <v>0</v>
       </c>
       <c r="ED20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG20" t="n">
-        <v>-1.661808614858435e-05</v>
+        <v>0.2006469187917476</v>
       </c>
       <c r="EH20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI20" t="n">
-        <v>-0.03391516116037453</v>
+        <v>-0.03356676119331643</v>
       </c>
       <c r="EJ20" t="n">
-        <v>-0.02492316413475851</v>
+        <v>-0.06021994674353744</v>
       </c>
       <c r="EK20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL20" t="n">
         <v>0</v>
       </c>
       <c r="EM20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN20" t="n">
         <v>0</v>
@@ -11676,46 +11676,46 @@
         <v>-0</v>
       </c>
       <c r="EP20" t="n">
-        <v>0.05047716562235082</v>
+        <v>0.1135436331762059</v>
       </c>
       <c r="EQ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER20" t="n">
-        <v>-0.08673432366434224</v>
+        <v>-0.05986646333385267</v>
       </c>
       <c r="ES20" t="n">
-        <v>0.1004827382937108</v>
+        <v>-0.03244833617190705</v>
       </c>
       <c r="ET20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU20" t="n">
         <v>0</v>
       </c>
       <c r="EV20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW20" t="n">
         <v>0</v>
       </c>
       <c r="EX20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY20" t="n">
-        <v>0.06283022070518648</v>
+        <v>0.2344171159129403</v>
       </c>
       <c r="EZ20" t="n">
         <v>0</v>
       </c>
       <c r="FA20" t="n">
-        <v>-0.08369018873682219</v>
+        <v>-0.1297286575581099</v>
       </c>
       <c r="FB20" t="n">
-        <v>0.02190161719298093</v>
+        <v>-0.03411389058439795</v>
       </c>
       <c r="FC20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD20" t="n">
         <v>0</v>
@@ -11727,46 +11727,46 @@
         <v>0</v>
       </c>
       <c r="FG20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH20" t="n">
-        <v>0.05941678116704303</v>
+        <v>0.1123909793276081</v>
       </c>
       <c r="FI20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ20" t="n">
-        <v>0.01588095675096045</v>
+        <v>0.07844988951381356</v>
       </c>
       <c r="FK20" t="n">
-        <v>-0.04108164447852088</v>
+        <v>-0.01751930145807183</v>
       </c>
       <c r="FL20" t="n">
         <v>0</v>
       </c>
       <c r="FM20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO20" t="n">
         <v>0</v>
       </c>
       <c r="FP20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ20" t="n">
-        <v>-0.00230800481226204</v>
+        <v>0.1427183356207509</v>
       </c>
       <c r="FR20" t="n">
         <v>0</v>
       </c>
       <c r="FS20" t="n">
-        <v>-0.04876600872004058</v>
+        <v>-0.07314472079688968</v>
       </c>
       <c r="FT20" t="n">
-        <v>0.02332196084833215</v>
+        <v>-0.01213214324558594</v>
       </c>
       <c r="FU20" t="n">
         <v>0</v>
@@ -11775,22 +11775,22 @@
         <v>0</v>
       </c>
       <c r="FW20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY20" t="n">
         <v>-0</v>
       </c>
       <c r="FZ20" t="n">
-        <v>0.07653023830897418</v>
+        <v>0.1669041671890789</v>
       </c>
       <c r="GA20" t="n">
         <v>-0</v>
       </c>
       <c r="GB20" t="n">
-        <v>0.1406764507148384</v>
+        <v>-0.03916270300614899</v>
       </c>
       <c r="GC20" t="n">
         <v>-0</v>
@@ -11805,7 +11805,7 @@
         <v>0</v>
       </c>
       <c r="GG20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
